--- a/results/ddPCR/SNV_data_final.xlsx
+++ b/results/ddPCR/SNV_data_final.xlsx
@@ -808,25 +808,25 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
         <v>14338</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0233053907719027</v>
+        <v>0.014980670395835</v>
       </c>
       <c r="K3" t="n">
-        <v>0.012734008591143</v>
+        <v>0.00684736533114082</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0391443002296177</v>
+        <v>0.028463953959153</v>
       </c>
       <c r="M3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>0.181336309108662</v>
+        <v>0.132514995117869</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -958,25 +958,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
         <v>15304</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0162982039221943</v>
+        <v>0.011203754426875</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00928786390051286</v>
+        <v>0.00558027384132161</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0265915759160815</v>
+        <v>0.0201286539910169</v>
       </c>
       <c r="M6" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1829587036069</v>
+        <v>0.130684788290643</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -1108,25 +1108,25 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
         <v>15738</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0213513725116461</v>
+        <v>0.00898801942952175</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0128314193601071</v>
+        <v>0.00387678678732244</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0334392399942709</v>
+        <v>0.0177474087423495</v>
       </c>
       <c r="M9" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>0.177913330791714</v>
+        <v>0.133434998093786</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -1258,25 +1258,25 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
         <v>12847</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0276114772495322</v>
+        <v>0.0189808321786135</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0157684407109785</v>
+        <v>0.00946889092927793</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0449086962779743</v>
+        <v>0.0340077465817157</v>
       </c>
       <c r="M12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="N12" t="n">
-        <v>0.186814042188838</v>
+        <v>0.132326613217093</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -1408,25 +1408,25 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
         <v>15126</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0186621307597542</v>
+        <v>0.01080238146856</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0111856681547179</v>
+        <v>0.00537653790091842</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0293277407501047</v>
+        <v>0.0194282926630308</v>
       </c>
       <c r="M15" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
-        <v>0.178500595001983</v>
+        <v>0.132222662964432</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -1558,28 +1558,28 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I18" t="n">
         <v>14257</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0360338172361366</v>
+        <v>0.0197539835907091</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0243904723061523</v>
+        <v>0.0114785096976505</v>
       </c>
       <c r="L18" t="n">
-        <v>0.051404643095835</v>
+        <v>0.0317535545732957</v>
       </c>
       <c r="M18" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>0.182366556779126</v>
+        <v>0.133267868415515</v>
       </c>
       <c r="O18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -1708,25 +1708,25 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
         <v>15981</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0457875808296672</v>
+        <v>0.0293006246977474</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0296179289828689</v>
+        <v>0.0167423240858397</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0676402608623092</v>
+        <v>0.0476112222951057</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N21" t="n">
-        <v>0.181465490269695</v>
+        <v>0.131406044678055</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -1858,25 +1858,25 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
         <v>13306</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0169349089231796</v>
+        <v>0.0150529697593257</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00774078159564324</v>
+        <v>0.00649657416500155</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0321755702611389</v>
+        <v>0.0296850342065332</v>
       </c>
       <c r="M24" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N24" t="n">
-        <v>0.187885164587404</v>
+        <v>0.135277318502931</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -2008,28 +2008,28 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I27" t="n">
         <v>13841</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0223008630185349</v>
+        <v>0.0193905150413679</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0139868948942902</v>
+        <v>0.0117299319373846</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0338756544861425</v>
+        <v>0.0302973928766213</v>
       </c>
       <c r="M27" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N27" t="n">
-        <v>0.180622787370855</v>
+        <v>0.130048406907015</v>
       </c>
       <c r="O27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -2158,25 +2158,25 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
         <v>12382</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0183129629560705</v>
+        <v>0.0126768704980234</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00973237673361428</v>
+        <v>0.00578849205942158</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0314207833629785</v>
+        <v>0.0241355061402762</v>
       </c>
       <c r="M30" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N30" t="n">
-        <v>0.185753513164271</v>
+        <v>0.137296074947504</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
@@ -2308,25 +2308,25 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I33" t="n">
         <v>14783</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0218599903536224</v>
+        <v>0.0202981924901943</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0119437790371019</v>
+        <v>0.0108017082859052</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0367191035829907</v>
+        <v>0.0347489776003866</v>
       </c>
       <c r="M33" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N33" t="n">
-        <v>0.182642224176419</v>
+        <v>0.128526009605628</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
@@ -2458,25 +2458,25 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I36" t="n">
         <v>13460</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0241615039986325</v>
+        <v>0.0214758720994433</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0142923982641166</v>
+        <v>0.012253874711098</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0383021270654418</v>
+        <v>0.0349772232484425</v>
       </c>
       <c r="M36" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N36" t="n">
-        <v>0.185735512630015</v>
+        <v>0.133729569093611</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I39" t="n">
         <v>13713</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0272554602962315</v>
+        <v>0.0241087171828034</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0176708712658278</v>
+        <v>0.0151774111394517</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0403048979031228</v>
+        <v>0.0364935506287756</v>
       </c>
       <c r="M39" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N39" t="n">
-        <v>0.18230875811274</v>
+        <v>0.131262305841173</v>
       </c>
       <c r="O39" t="b">
         <v>1</v>
@@ -2758,25 +2758,25 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I42" t="n">
         <v>13607</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0412730401712983</v>
+        <v>0.0312613788575185</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0283061106799995</v>
+        <v>0.0201687945039585</v>
       </c>
       <c r="L42" t="n">
-        <v>0.0582441339406568</v>
+        <v>0.0463481439917334</v>
       </c>
       <c r="M42" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N42" t="n">
-        <v>0.183728963033733</v>
+        <v>0.132284853384287</v>
       </c>
       <c r="O42" t="b">
         <v>1</v>
@@ -2908,25 +2908,25 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I45" t="n">
         <v>14290</v>
       </c>
       <c r="J45" t="n">
-        <v>0.036506625952017</v>
+        <v>0.0322085971591359</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0251329570604643</v>
+        <v>0.0216128516105472</v>
       </c>
       <c r="L45" t="n">
-        <v>0.0513863254942307</v>
+        <v>0.0462983063231596</v>
       </c>
       <c r="M45" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N45" t="n">
-        <v>0.181945416375087</v>
+        <v>0.13296011196641</v>
       </c>
       <c r="O45" t="b">
         <v>1</v>
@@ -3508,25 +3508,25 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I57" t="n">
         <v>15148</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0253407938824796</v>
+        <v>0.0135135642408907</v>
       </c>
       <c r="K57" t="n">
-        <v>0.014176421772879</v>
+        <v>0.00583254843947606</v>
       </c>
       <c r="L57" t="n">
-        <v>0.0418318880093086</v>
+        <v>0.0266455108389331</v>
       </c>
       <c r="M57" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N57" t="n">
-        <v>0.178241351993663</v>
+        <v>0.132030631106417</v>
       </c>
       <c r="O57" t="b">
         <v>0</v>
@@ -3658,25 +3658,25 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I60" t="n">
         <v>14491</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0694928046766883</v>
+        <v>0.0453198322982167</v>
       </c>
       <c r="K60" t="n">
-        <v>0.0440445784872276</v>
+        <v>0.0253619154904362</v>
       </c>
       <c r="L60" t="n">
-        <v>0.104306864255649</v>
+        <v>0.0747685835913965</v>
       </c>
       <c r="M60" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N60" t="n">
-        <v>0.179421710026913</v>
+        <v>0.131115865019667</v>
       </c>
       <c r="O60" t="b">
         <v>0</v>
@@ -3808,25 +3808,25 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I63" t="n">
         <v>14590</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0296125027897504</v>
+        <v>0.019739555436586</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0175386137638802</v>
+        <v>0.0101947209601838</v>
       </c>
       <c r="L63" t="n">
-        <v>0.0468537927773455</v>
+        <v>0.0345147643521291</v>
       </c>
       <c r="M63" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N63" t="n">
-        <v>0.185058259081563</v>
+        <v>0.130226182316655</v>
       </c>
       <c r="O63" t="b">
         <v>0</v>
@@ -3958,25 +3958,25 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I66" t="n">
         <v>14618</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0272588024536015</v>
+        <v>0.0129773484671154</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0168466402173342</v>
+        <v>0.00621744590848579</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0417720765293867</v>
+        <v>0.0239110335195548</v>
       </c>
       <c r="M66" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N66" t="n">
-        <v>0.184703789848132</v>
+        <v>0.129976741004241</v>
       </c>
       <c r="O66" t="b">
         <v>0</v>
@@ -4108,25 +4108,25 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I69" t="n">
         <v>15162</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0233024710818405</v>
+        <v>0.0201947696961061</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0130345378482211</v>
+        <v>0.0107471811020912</v>
       </c>
       <c r="L69" t="n">
-        <v>0.0384752462338496</v>
+        <v>0.0345689175690832</v>
       </c>
       <c r="M69" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N69" t="n">
-        <v>0.178076770874555</v>
+        <v>0.131908719166337</v>
       </c>
       <c r="O69" t="b">
         <v>0</v>
@@ -4258,25 +4258,25 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I72" t="n">
         <v>14857</v>
       </c>
       <c r="J72" t="n">
-        <v>0.0213034770890677</v>
+        <v>0.0106503627498455</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0116392936652112</v>
+        <v>0.00428043455186239</v>
       </c>
       <c r="L72" t="n">
-        <v>0.0357865862556872</v>
+        <v>0.0219645406716706</v>
       </c>
       <c r="M72" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N72" t="n">
-        <v>0.181732516658814</v>
+        <v>0.134616679006529</v>
       </c>
       <c r="O72" t="b">
         <v>0</v>
@@ -4373,10 +4373,10 @@
         <v>0.0395112628427656</v>
       </c>
       <c r="M74" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N74" t="n">
-        <v>0.130463144161774</v>
+        <v>0.122309197651663</v>
       </c>
       <c r="O74" t="b">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0.0396867753506377</v>
       </c>
       <c r="M80" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N80" t="n">
-        <v>0.1306015835442</v>
+        <v>0.122438984572688</v>
       </c>
       <c r="O80" t="b">
         <v>0</v>
@@ -4823,10 +4823,10 @@
         <v>0.0318750230176824</v>
       </c>
       <c r="M83" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N83" t="n">
-        <v>0.125217391304348</v>
+        <v>0.118260869565217</v>
       </c>
       <c r="O83" t="b">
         <v>0</v>
@@ -4973,10 +4973,10 @@
         <v>0.0474790543977189</v>
       </c>
       <c r="M86" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N86" t="n">
-        <v>0.124317977760895</v>
+        <v>0.117411423440845</v>
       </c>
       <c r="O86" t="b">
         <v>0</v>
@@ -5123,10 +5123,10 @@
         <v>0.117633304299542</v>
       </c>
       <c r="M89" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N89" t="n">
-        <v>0.127551020408163</v>
+        <v>0.119579081632653</v>
       </c>
       <c r="O89" t="b">
         <v>0</v>
@@ -5273,10 +5273,10 @@
         <v>0.0649899108938712</v>
       </c>
       <c r="M92" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N92" t="n">
-        <v>0.130039011703511</v>
+        <v>0.121911573472042</v>
       </c>
       <c r="O92" t="b">
         <v>0</v>
@@ -5423,10 +5423,10 @@
         <v>0.057776992013009</v>
       </c>
       <c r="M95" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N95" t="n">
-        <v>0.128838307923556</v>
+        <v>0.121680624150025</v>
       </c>
       <c r="O95" t="b">
         <v>0</v>
@@ -5573,10 +5573,10 @@
         <v>0.0183983169247508</v>
       </c>
       <c r="M98" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N98" t="n">
-        <v>0.136239782016349</v>
+        <v>0.126508369015181</v>
       </c>
       <c r="O98" t="b">
         <v>0</v>
@@ -6008,25 +6008,25 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I107" t="n">
         <v>14658</v>
       </c>
       <c r="J107" t="n">
-        <v>0.0308123981225857</v>
+        <v>0.00648507799825611</v>
       </c>
       <c r="K107" t="n">
-        <v>0.0185380001061702</v>
+        <v>0.00176664092441785</v>
       </c>
       <c r="L107" t="n">
-        <v>0.048174542842082</v>
+        <v>0.0166160383348421</v>
       </c>
       <c r="M107" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N107" t="n">
-        <v>0.129622049392823</v>
+        <v>0.0545777050075044</v>
       </c>
       <c r="O107" t="b">
         <v>0</v>
@@ -6058,25 +6058,25 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>12446</v>
+        <v>12415</v>
       </c>
       <c r="I108" t="n">
         <v>14851</v>
       </c>
       <c r="J108" t="n">
-        <v>49.522313199991</v>
+        <v>49.3458379560325</v>
       </c>
       <c r="K108" t="n">
-        <v>48.8072893477608</v>
+        <v>48.6311259933592</v>
       </c>
       <c r="L108" t="n">
-        <v>50.2375204822756</v>
+        <v>50.0608009562622</v>
       </c>
       <c r="M108" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N108" t="n">
-        <v>0.168338832401858</v>
+        <v>0.101003299441115</v>
       </c>
       <c r="O108" t="b">
         <v>1</v>
@@ -6158,25 +6158,25 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I110" t="n">
         <v>12684</v>
       </c>
       <c r="J110" t="n">
-        <v>0.0274625604166598</v>
+        <v>0.00998537433955325</v>
       </c>
       <c r="K110" t="n">
-        <v>0.0137056667207351</v>
+        <v>0.00272040401502706</v>
       </c>
       <c r="L110" t="n">
-        <v>0.0491654979511009</v>
+        <v>0.0255768708023774</v>
       </c>
       <c r="M110" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N110" t="n">
-        <v>0.134027120782088</v>
+        <v>0.0551876379690949</v>
       </c>
       <c r="O110" t="b">
         <v>0</v>
@@ -6208,25 +6208,25 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>11077</v>
+        <v>11055</v>
       </c>
       <c r="I111" t="n">
         <v>14565</v>
       </c>
       <c r="J111" t="n">
-        <v>49.4710277833295</v>
+        <v>49.3608240008652</v>
       </c>
       <c r="K111" t="n">
-        <v>48.7522224280668</v>
+        <v>48.6419830807987</v>
       </c>
       <c r="L111" t="n">
-        <v>50.1900361166195</v>
+        <v>50.079910187013</v>
       </c>
       <c r="M111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N111" t="n">
-        <v>0.17164435290079</v>
+        <v>0.102986611740474</v>
       </c>
       <c r="O111" t="b">
         <v>1</v>
@@ -6308,25 +6308,25 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I113" t="n">
         <v>16424</v>
       </c>
       <c r="J113" t="n">
-        <v>0.0287777175725828</v>
+        <v>0.00479524545014865</v>
       </c>
       <c r="K113" t="n">
-        <v>0.0170476765189387</v>
+        <v>0.00098880598307684</v>
       </c>
       <c r="L113" t="n">
-        <v>0.0455175900658343</v>
+        <v>0.0140200200272568</v>
       </c>
       <c r="M113" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="N113" t="n">
-        <v>0.127861665854847</v>
+        <v>0.0487092060399415</v>
       </c>
       <c r="O113" t="b">
         <v>0</v>
@@ -6358,25 +6358,25 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>12570</v>
+        <v>12547</v>
       </c>
       <c r="I114" t="n">
         <v>14952</v>
       </c>
       <c r="J114" t="n">
-        <v>49.8568157448099</v>
+        <v>49.7256918669047</v>
       </c>
       <c r="K114" t="n">
-        <v>49.1439644279967</v>
+        <v>49.0130581687174</v>
       </c>
       <c r="L114" t="n">
-        <v>50.5697216945511</v>
+        <v>50.4384301812088</v>
       </c>
       <c r="M114" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N114" t="n">
-        <v>0.167201712145532</v>
+        <v>0.100321027287319</v>
       </c>
       <c r="O114" t="b">
         <v>1</v>
@@ -6508,25 +6508,25 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>13539</v>
+        <v>13620</v>
       </c>
       <c r="I117" t="n">
         <v>14995</v>
       </c>
       <c r="J117" t="n">
-        <v>48.9392123277984</v>
+        <v>49.5452777427023</v>
       </c>
       <c r="K117" t="n">
-        <v>48.1895635920623</v>
+        <v>48.7924293637114</v>
       </c>
       <c r="L117" t="n">
-        <v>49.6892876469678</v>
+        <v>50.2983094443618</v>
       </c>
       <c r="M117" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="N117" t="n">
-        <v>0.166722240746916</v>
+        <v>0.106702234078026</v>
       </c>
       <c r="O117" t="b">
         <v>1</v>
@@ -6558,28 +6558,28 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I118" t="n">
         <v>14947</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0421882692699502</v>
+        <v>0.0295266258802269</v>
       </c>
       <c r="K118" t="n">
-        <v>0.0284249561941018</v>
+        <v>0.0182576124474703</v>
       </c>
       <c r="L118" t="n">
-        <v>0.060347244451351</v>
+        <v>0.0452130833974063</v>
       </c>
       <c r="M118" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="N118" t="n">
-        <v>0.220780089650097</v>
+        <v>0.12711580919248</v>
       </c>
       <c r="O118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P118" t="b">
         <v>0</v>
@@ -6658,25 +6658,25 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>14220</v>
+        <v>14319</v>
       </c>
       <c r="I120" t="n">
         <v>16377</v>
       </c>
       <c r="J120" t="n">
-        <v>49.4798545342186</v>
+        <v>50.0526511157181</v>
       </c>
       <c r="K120" t="n">
-        <v>48.7888935509672</v>
+        <v>49.3600758378679</v>
       </c>
       <c r="L120" t="n">
-        <v>50.1710005821088</v>
+        <v>50.7452076114145</v>
       </c>
       <c r="M120" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N120" t="n">
-        <v>0.164865359956036</v>
+        <v>0.103804115527874</v>
       </c>
       <c r="O120" t="b">
         <v>1</v>
@@ -6708,28 +6708,28 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I121" t="n">
         <v>15758</v>
       </c>
       <c r="J121" t="n">
-        <v>0.0436262258461236</v>
+        <v>0.0323632642888451</v>
       </c>
       <c r="K121" t="n">
-        <v>0.0296086064938902</v>
+        <v>0.020496654908091</v>
       </c>
       <c r="L121" t="n">
-        <v>0.0620254517390772</v>
+        <v>0.0486313404657064</v>
       </c>
       <c r="M121" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N121" t="n">
-        <v>0.21576342175403</v>
+        <v>0.126919659855312</v>
       </c>
       <c r="O121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P121" t="b">
         <v>0</v>
@@ -6808,25 +6808,25 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>16383</v>
+        <v>16434</v>
       </c>
       <c r="I123" t="n">
         <v>17378</v>
       </c>
       <c r="J123" t="n">
-        <v>49.4439060989646</v>
+        <v>49.8996043885338</v>
       </c>
       <c r="K123" t="n">
-        <v>48.687658469767</v>
+        <v>49.139483664773</v>
       </c>
       <c r="L123" t="n">
-        <v>50.2003485847566</v>
+        <v>50.6597602051396</v>
       </c>
       <c r="M123" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="N123" t="n">
-        <v>0.166877661410979</v>
+        <v>0.0978248359995396</v>
       </c>
       <c r="O123" t="b">
         <v>1</v>
@@ -6858,28 +6858,28 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I124" t="n">
         <v>16883</v>
       </c>
       <c r="J124" t="n">
-        <v>0.0387412092419189</v>
+        <v>0.0296213042113514</v>
       </c>
       <c r="K124" t="n">
-        <v>0.0267810944497871</v>
+        <v>0.0193203992079932</v>
       </c>
       <c r="L124" t="n">
-        <v>0.0542727061453484</v>
+        <v>0.043499603851126</v>
       </c>
       <c r="M124" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="N124" t="n">
-        <v>0.213232245454007</v>
+        <v>0.124385476514837</v>
       </c>
       <c r="O124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P124" t="b">
         <v>0</v>
@@ -7408,25 +7408,25 @@
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I135" t="n">
         <v>14951</v>
       </c>
       <c r="J135" t="n">
-        <v>0.0178139456489367</v>
+        <v>0.00593709791742938</v>
       </c>
       <c r="K135" t="n">
-        <v>0.00919917687437099</v>
+        <v>0.00161730327749761</v>
       </c>
       <c r="L135" t="n">
-        <v>0.0311544524251847</v>
+        <v>0.0152140469181478</v>
       </c>
       <c r="M135" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="N135" t="n">
-        <v>0.207343990368537</v>
+        <v>0.113704768911778</v>
       </c>
       <c r="O135" t="b">
         <v>0</v>
@@ -7558,25 +7558,25 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I138" t="n">
         <v>16472</v>
       </c>
       <c r="J138" t="n">
-        <v>0.029121261860557</v>
+        <v>0.0164569280588581</v>
       </c>
       <c r="K138" t="n">
-        <v>0.0184406124345585</v>
+        <v>0.00875640873553979</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0437694383986565</v>
+        <v>0.0281797678981566</v>
       </c>
       <c r="M138" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="N138" t="n">
-        <v>0.200339970859641</v>
+        <v>0.109276347741622</v>
       </c>
       <c r="O138" t="b">
         <v>0</v>
@@ -7858,25 +7858,25 @@
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I144" t="n">
         <v>28515</v>
       </c>
       <c r="J144" t="n">
-        <v>0.0258880305513094</v>
+        <v>0.0135058648073245</v>
       </c>
       <c r="K144" t="n">
-        <v>0.0164076826489984</v>
+        <v>0.00697786121276028</v>
       </c>
       <c r="L144" t="n">
-        <v>0.0388571205242508</v>
+        <v>0.0235978934844846</v>
       </c>
       <c r="M144" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N144" t="n">
-        <v>0.189374013677012</v>
+        <v>0.119235490092934</v>
       </c>
       <c r="O144" t="b">
         <v>0</v>
@@ -8008,25 +8008,25 @@
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="I147" t="n">
         <v>45458</v>
       </c>
       <c r="J147" t="n">
-        <v>0.0487487402777115</v>
+        <v>0.0237803171174049</v>
       </c>
       <c r="K147" t="n">
-        <v>0.0349814030312327</v>
+        <v>0.0145252895048298</v>
       </c>
       <c r="L147" t="n">
-        <v>0.0661382814873186</v>
+        <v>0.0367288965082101</v>
       </c>
       <c r="M147" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="N147" t="n">
-        <v>0.180386290641911</v>
+        <v>0.15178846407673</v>
       </c>
       <c r="O147" t="b">
         <v>0</v>
@@ -8158,19 +8158,19 @@
         <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I150" t="n">
         <v>33901</v>
       </c>
       <c r="J150" t="n">
-        <v>0.0292032320188871</v>
+        <v>0.0269570375257602</v>
       </c>
       <c r="K150" t="n">
-        <v>0.0155497795674647</v>
+        <v>0.0139293538041376</v>
       </c>
       <c r="L150" t="n">
-        <v>0.049938766131247</v>
+        <v>0.0470888435165543</v>
       </c>
       <c r="M150" t="n">
         <v>58</v>
@@ -8308,25 +8308,25 @@
         <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="I153" t="n">
         <v>43094</v>
       </c>
       <c r="J153" t="n">
-        <v>0.344794475988208</v>
+        <v>0.314507563935298</v>
       </c>
       <c r="K153" t="n">
-        <v>0.310690395479153</v>
+        <v>0.281988600584221</v>
       </c>
       <c r="L153" t="n">
-        <v>0.381646234605009</v>
+        <v>0.349772198537191</v>
       </c>
       <c r="M153" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="N153" t="n">
-        <v>0.180999675128788</v>
+        <v>0.153153571262821</v>
       </c>
       <c r="O153" t="b">
         <v>1</v>
@@ -8458,25 +8458,25 @@
         <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I156" t="n">
         <v>30531</v>
       </c>
       <c r="J156" t="n">
-        <v>0.0253301119570894</v>
+        <v>0.011959316978027</v>
       </c>
       <c r="K156" t="n">
-        <v>0.0177286653753564</v>
+        <v>0.00696385745710321</v>
       </c>
       <c r="L156" t="n">
-        <v>0.0351023107693766</v>
+        <v>0.0191620728414811</v>
       </c>
       <c r="M156" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="N156" t="n">
-        <v>0.186695489830009</v>
+        <v>0.117912940945269</v>
       </c>
       <c r="O156" t="b">
         <v>0</v>
@@ -8623,13 +8623,13 @@
         <v>0.0470525567441698</v>
       </c>
       <c r="M159" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N159" t="n">
-        <v>0.166164071635178</v>
+        <v>0.104621822881408</v>
       </c>
       <c r="O159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P159" t="b">
         <v>0</v>
@@ -8658,28 +8658,28 @@
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I160" t="n">
         <v>15505</v>
       </c>
       <c r="J160" t="n">
-        <v>0.041943674711813</v>
+        <v>0.0318153710784323</v>
       </c>
       <c r="K160" t="n">
-        <v>0.0280606679562819</v>
+        <v>0.0199210428400008</v>
       </c>
       <c r="L160" t="n">
-        <v>0.0603325997430713</v>
+        <v>0.0482364727976939</v>
       </c>
       <c r="M160" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N160" t="n">
-        <v>0.219284101902612</v>
+        <v>0.128990648178007</v>
       </c>
       <c r="O160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P160" t="b">
         <v>0</v>
@@ -8773,13 +8773,13 @@
         <v>0.0372117442661138</v>
       </c>
       <c r="M162" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="N162" t="n">
-        <v>0.167989341365927</v>
+        <v>0.0984765104558883</v>
       </c>
       <c r="O162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P162" t="b">
         <v>0</v>
@@ -8808,25 +8808,25 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I163" t="n">
         <v>15361</v>
       </c>
       <c r="J163" t="n">
-        <v>0.0329872541122533</v>
+        <v>0.0190955606776129</v>
       </c>
       <c r="K163" t="n">
-        <v>0.0198507402173729</v>
+        <v>0.00952933327118961</v>
       </c>
       <c r="L163" t="n">
-        <v>0.0515569753728843</v>
+        <v>0.034190662690026</v>
       </c>
       <c r="M163" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="N163" t="n">
-        <v>0.221339756526268</v>
+        <v>0.12368986394115</v>
       </c>
       <c r="O163" t="b">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0.0834289415080774</v>
       </c>
       <c r="M165" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N165" t="n">
-        <v>0.169284940411701</v>
+        <v>0.101570964247021</v>
       </c>
       <c r="O165" t="b">
         <v>1</v>
@@ -8958,25 +8958,25 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I166" t="n">
         <v>15473</v>
       </c>
       <c r="J166" t="n">
-        <v>0.0527941479753464</v>
+        <v>0.0406079507450444</v>
       </c>
       <c r="K166" t="n">
-        <v>0.0344729251470512</v>
+        <v>0.0247960204815322</v>
       </c>
       <c r="L166" t="n">
-        <v>0.0774055627616135</v>
+        <v>0.0627521509651415</v>
       </c>
       <c r="M166" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N166" t="n">
-        <v>0.219737607445227</v>
+        <v>0.129257416144251</v>
       </c>
       <c r="O166" t="b">
         <v>0</v>
@@ -9073,10 +9073,10 @@
         <v>0.0363094412112625</v>
       </c>
       <c r="M168" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="N168" t="n">
-        <v>0.163618301875767</v>
+        <v>0.0993396832817156</v>
       </c>
       <c r="O168" t="b">
         <v>1</v>
@@ -9108,25 +9108,25 @@
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I169" t="n">
         <v>14985</v>
       </c>
       <c r="J169" t="n">
-        <v>0.0280308282249062</v>
+        <v>0.0190169150434904</v>
       </c>
       <c r="K169" t="n">
-        <v>0.0185225823251647</v>
+        <v>0.0114004383969163</v>
       </c>
       <c r="L169" t="n">
-        <v>0.0408010525023608</v>
+        <v>0.0298787830593968</v>
       </c>
       <c r="M169" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="N169" t="n">
-        <v>0.22022022022022</v>
+        <v>0.126793460126793</v>
       </c>
       <c r="O169" t="b">
         <v>0</v>
@@ -9223,10 +9223,10 @@
         <v>0.0310160099927389</v>
       </c>
       <c r="M171" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="N171" t="n">
-        <v>0.164941417358662</v>
+        <v>0.102377431463997</v>
       </c>
       <c r="O171" t="b">
         <v>1</v>
@@ -9258,25 +9258,25 @@
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="I172" t="n">
         <v>14731</v>
       </c>
       <c r="J172" t="n">
-        <v>0.039123191308611</v>
+        <v>0.0214145601225145</v>
       </c>
       <c r="K172" t="n">
-        <v>0.0278446488132155</v>
+        <v>0.0134592778401782</v>
       </c>
       <c r="L172" t="n">
-        <v>0.0535843915097773</v>
+        <v>0.0324661689099071</v>
       </c>
       <c r="M172" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="N172" t="n">
-        <v>0.217228972914262</v>
+        <v>0.128979702667843</v>
       </c>
       <c r="O172" t="b">
         <v>1</v>
@@ -9358,25 +9358,25 @@
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="I174" t="n">
         <v>11805</v>
       </c>
       <c r="J174" t="n">
-        <v>0.0529247773625348</v>
+        <v>0.0258298569646239</v>
       </c>
       <c r="K174" t="n">
-        <v>0.0378631805412595</v>
+        <v>0.0158732702078957</v>
       </c>
       <c r="L174" t="n">
-        <v>0.0721814907387254</v>
+        <v>0.0398535591816107</v>
       </c>
       <c r="M174" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="N174" t="n">
-        <v>0.211774671749259</v>
+        <v>0.118593816179585</v>
       </c>
       <c r="O174" t="b">
         <v>1</v>
@@ -10058,25 +10058,25 @@
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I188" t="n">
         <v>15577</v>
       </c>
       <c r="J188" t="n">
-        <v>0.0201027975727675</v>
+        <v>0.00211530942344793</v>
       </c>
       <c r="K188" t="n">
-        <v>0.0120725452512975</v>
+        <v>0.000256109714600119</v>
       </c>
       <c r="L188" t="n">
-        <v>0.0315147097116245</v>
+        <v>0.00765597021162884</v>
       </c>
       <c r="M188" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N188" t="n">
-        <v>0.128394427681839</v>
+        <v>0.0513577710727354</v>
       </c>
       <c r="O188" t="b">
         <v>0</v>
@@ -10108,25 +10108,25 @@
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I189" t="n">
         <v>13585</v>
       </c>
       <c r="J189" t="n">
-        <v>0.0205532481101835</v>
+        <v>0.00256829372228805</v>
       </c>
       <c r="K189" t="n">
-        <v>0.011724431213468</v>
+        <v>0.000310961545384949</v>
       </c>
       <c r="L189" t="n">
-        <v>0.0334873343957439</v>
+        <v>0.00929384058519126</v>
       </c>
       <c r="M189" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="N189" t="n">
-        <v>0.169304379830696</v>
+        <v>0.103054839896945</v>
       </c>
       <c r="O189" t="b">
         <v>0</v>
@@ -10158,25 +10158,25 @@
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I190" t="n">
         <v>14238</v>
       </c>
       <c r="J190" t="n">
-        <v>0.0298094341612826</v>
+        <v>0.0206333898245615</v>
       </c>
       <c r="K190" t="n">
-        <v>0.0194018542293971</v>
+        <v>0.0121942266214877</v>
       </c>
       <c r="L190" t="n">
-        <v>0.0438960167256973</v>
+        <v>0.0327506659825427</v>
       </c>
       <c r="M190" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N190" t="n">
-        <v>0.217727208877651</v>
+        <v>0.126422250316056</v>
       </c>
       <c r="O190" t="b">
         <v>0</v>
@@ -10208,25 +10208,25 @@
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I191" t="n">
         <v>14403</v>
       </c>
       <c r="J191" t="n">
-        <v>0.0314548904273985</v>
+        <v>0.00331001809106343</v>
       </c>
       <c r="K191" t="n">
-        <v>0.0189244247804</v>
+        <v>0.000400826951868484</v>
       </c>
       <c r="L191" t="n">
-        <v>0.0491795973805057</v>
+        <v>0.0119640727747862</v>
       </c>
       <c r="M191" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N191" t="n">
-        <v>0.131916961744081</v>
+        <v>0.0555439838922447</v>
       </c>
       <c r="O191" t="b">
         <v>0</v>
@@ -10258,25 +10258,25 @@
         <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I192" t="n">
         <v>14916</v>
       </c>
       <c r="J192" t="n">
-        <v>0.0185206740166986</v>
+        <v>0.00841764493194188</v>
       </c>
       <c r="K192" t="n">
-        <v>0.00924181418395213</v>
+        <v>0.00273265264926011</v>
       </c>
       <c r="L192" t="n">
-        <v>0.0331658435081509</v>
+        <v>0.0196564531513527</v>
       </c>
       <c r="M192" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N192" t="n">
-        <v>0.167605256100831</v>
+        <v>0.100563153660499</v>
       </c>
       <c r="O192" t="b">
         <v>0</v>
@@ -10308,25 +10308,25 @@
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I193" t="n">
         <v>13475</v>
       </c>
       <c r="J193" t="n">
-        <v>0.0510751842091668</v>
+        <v>0.0291792001378021</v>
       </c>
       <c r="K193" t="n">
-        <v>0.0339081130724099</v>
+        <v>0.0166681211204926</v>
       </c>
       <c r="L193" t="n">
-        <v>0.0739195593852965</v>
+        <v>0.0474375905400549</v>
       </c>
       <c r="M193" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N193" t="n">
-        <v>0.222634508348794</v>
+        <v>0.126159554730983</v>
       </c>
       <c r="O193" t="b">
         <v>0</v>
@@ -10508,25 +10508,25 @@
         <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I197" t="n">
         <v>11528</v>
       </c>
       <c r="J197" t="n">
-        <v>0.0202725454478498</v>
+        <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>0.0101113768569237</v>
+        <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0.0363351511319709</v>
+        <v>0.00680172560875792</v>
       </c>
       <c r="M197" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N197" t="n">
-        <v>0.138792505204719</v>
+        <v>0.0520471894517696</v>
       </c>
       <c r="O197" t="b">
         <v>0</v>
@@ -10558,25 +10558,25 @@
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I198" t="n">
         <v>15243</v>
       </c>
       <c r="J198" t="n">
-        <v>0.0123344798103813</v>
+        <v>0.00685196508433168</v>
       </c>
       <c r="K198" t="n">
-        <v>0.00563690125803689</v>
+        <v>0.00222407823331548</v>
       </c>
       <c r="L198" t="n">
-        <v>0.0234444253547985</v>
+        <v>0.0160070256151745</v>
       </c>
       <c r="M198" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N198" t="n">
-        <v>0.170570097749787</v>
+        <v>0.104966213999869</v>
       </c>
       <c r="O198" t="b">
         <v>0</v>
@@ -10608,25 +10608,25 @@
         <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I199" t="n">
         <v>13601</v>
       </c>
       <c r="J199" t="n">
-        <v>0.042355124818436</v>
+        <v>0.0188185400492371</v>
       </c>
       <c r="K199" t="n">
-        <v>0.0278745408868077</v>
+        <v>0.00971646679215492</v>
       </c>
       <c r="L199" t="n">
-        <v>0.0617487404510505</v>
+        <v>0.0329207350989509</v>
       </c>
       <c r="M199" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N199" t="n">
-        <v>0.220572016763473</v>
+        <v>0.132343210058084</v>
       </c>
       <c r="O199" t="b">
         <v>0</v>
@@ -10808,25 +10808,25 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I203" t="n">
         <v>16235</v>
       </c>
       <c r="J203" t="n">
-        <v>0.0365272748131108</v>
+        <v>0.0121734709047366</v>
       </c>
       <c r="K203" t="n">
-        <v>0.0226012344665309</v>
+        <v>0.00489348041321926</v>
       </c>
       <c r="L203" t="n">
-        <v>0.0558760373993227</v>
+        <v>0.0250941652340722</v>
       </c>
       <c r="M203" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="N203" t="n">
-        <v>0.129350169387127</v>
+        <v>0.0492762550046196</v>
       </c>
       <c r="O203" t="b">
         <v>0</v>
@@ -10858,25 +10858,25 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I204" t="n">
         <v>14544</v>
       </c>
       <c r="J204" t="n">
-        <v>0.0191367607595444</v>
+        <v>0.00574041535638117</v>
       </c>
       <c r="K204" t="n">
-        <v>0.00917420008474224</v>
+        <v>0.00118370772244247</v>
       </c>
       <c r="L204" t="n">
-        <v>0.0352154000918325</v>
+        <v>0.0167832927831602</v>
       </c>
       <c r="M204" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N204" t="n">
-        <v>0.171892189218922</v>
+        <v>0.103135313531353</v>
       </c>
       <c r="O204" t="b">
         <v>0</v>
@@ -10908,25 +10908,25 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I205" t="n">
         <v>14400</v>
       </c>
       <c r="J205" t="n">
-        <v>0.0432034700276295</v>
+        <v>0.0287994560170482</v>
       </c>
       <c r="K205" t="n">
-        <v>0.0267320571429448</v>
+        <v>0.0157398604822795</v>
       </c>
       <c r="L205" t="n">
-        <v>0.0660890690420469</v>
+        <v>0.0483506650330483</v>
       </c>
       <c r="M205" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N205" t="n">
-        <v>0.222222222222222</v>
+        <v>0.125</v>
       </c>
       <c r="O205" t="b">
         <v>0</v>
@@ -11358,19 +11358,19 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I214" t="n">
         <v>13049</v>
       </c>
       <c r="J214" t="n">
-        <v>0.00581523512614679</v>
+        <v>0.00290747925075432</v>
       </c>
       <c r="K214" t="n">
-        <v>0.00158377210450415</v>
+        <v>0.000352048273634993</v>
       </c>
       <c r="L214" t="n">
-        <v>0.0149129635684909</v>
+        <v>0.0105168790929558</v>
       </c>
       <c r="M214" t="n">
         <v>7</v>
@@ -11508,19 +11508,19 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I217" t="n">
         <v>13973</v>
       </c>
       <c r="J217" t="n">
-        <v>0.00889625015698359</v>
+        <v>0.00323437261539804</v>
       </c>
       <c r="K217" t="n">
-        <v>0.00432327699596529</v>
+        <v>0.000872073747399335</v>
       </c>
       <c r="L217" t="n">
-        <v>0.0163044049483267</v>
+        <v>0.00842681281661274</v>
       </c>
       <c r="M217" t="n">
         <v>7</v>
@@ -11529,7 +11529,7 @@
         <v>0.0500966149001646</v>
       </c>
       <c r="O217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P217" t="b">
         <v>0</v>
@@ -11558,25 +11558,25 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I218" t="n">
         <v>13975</v>
       </c>
       <c r="J218" t="n">
-        <v>0.0234200271939498</v>
+        <v>0.00900642178539508</v>
       </c>
       <c r="K218" t="n">
-        <v>0.0124642346931522</v>
+        <v>0.00292375375220035</v>
       </c>
       <c r="L218" t="n">
-        <v>0.0400860433490615</v>
+        <v>0.0210321426341526</v>
       </c>
       <c r="M218" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N218" t="n">
-        <v>0.128801431127013</v>
+        <v>0.0500894454382826</v>
       </c>
       <c r="O218" t="b">
         <v>0</v>
@@ -11608,28 +11608,28 @@
         <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="I219" t="n">
         <v>15002</v>
       </c>
       <c r="J219" t="n">
-        <v>0.065050894923004</v>
+        <v>0.0158574664754128</v>
       </c>
       <c r="K219" t="n">
-        <v>0.0466282066092796</v>
+        <v>0.00760106298599994</v>
       </c>
       <c r="L219" t="n">
-        <v>0.0883884732041128</v>
+        <v>0.0291890833673821</v>
       </c>
       <c r="M219" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="N219" t="n">
-        <v>0.166644447407012</v>
+        <v>0.106652446340488</v>
       </c>
       <c r="O219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P219" t="b">
         <v>0</v>
@@ -11658,28 +11658,28 @@
         <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I220" t="n">
         <v>13399</v>
       </c>
       <c r="J220" t="n">
-        <v>0.0557748484125098</v>
+        <v>0.0365355198401313</v>
       </c>
       <c r="K220" t="n">
-        <v>0.0373224382310614</v>
+        <v>0.0219831622279946</v>
       </c>
       <c r="L220" t="n">
-        <v>0.0802015351358053</v>
+        <v>0.0571146656847876</v>
       </c>
       <c r="M220" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N220" t="n">
-        <v>0.223897305769087</v>
+        <v>0.126875139935816</v>
       </c>
       <c r="O220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P220" t="b">
         <v>0</v>
@@ -11808,19 +11808,19 @@
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I223" t="n">
         <v>14207</v>
       </c>
       <c r="J223" t="n">
-        <v>0.00139669643417131</v>
+        <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>0.0000353596939840814</v>
+        <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>0.00778912828769894</v>
+        <v>0.00515606907987275</v>
       </c>
       <c r="M223" t="n">
         <v>7</v>
@@ -11958,19 +11958,19 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I226" t="n">
         <v>11101</v>
       </c>
       <c r="J226" t="n">
-        <v>0.00241184462561569</v>
+        <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>0.0000610604465733903</v>
+        <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0.0134447531881521</v>
+        <v>0.00890053330757223</v>
       </c>
       <c r="M226" t="n">
         <v>6</v>
@@ -12008,19 +12008,19 @@
         <v>1</v>
       </c>
       <c r="H227" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I227" t="n">
         <v>32348</v>
       </c>
       <c r="J227" t="n">
-        <v>0.0177584334222314</v>
+        <v>0.00564978437995209</v>
       </c>
       <c r="K227" t="n">
-        <v>0.0111261405480592</v>
+        <v>0.00227125831523021</v>
       </c>
       <c r="L227" t="n">
-        <v>0.0268984672489547</v>
+        <v>0.0116441429437625</v>
       </c>
       <c r="M227" t="n">
         <v>42</v>
@@ -12058,25 +12058,25 @@
         <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I228" t="n">
         <v>31192</v>
       </c>
       <c r="J228" t="n">
-        <v>0.0204577050235253</v>
+        <v>0.012785201264778</v>
       </c>
       <c r="K228" t="n">
-        <v>0.0131039531994536</v>
+        <v>0.00715434070315364</v>
       </c>
       <c r="L228" t="n">
-        <v>0.0304533685920239</v>
+        <v>0.0210952844022331</v>
       </c>
       <c r="M228" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="N228" t="n">
-        <v>0.153885611695306</v>
+        <v>0.0929725570659143</v>
       </c>
       <c r="O228" t="b">
         <v>0</v>
@@ -12108,25 +12108,25 @@
         <v>1</v>
       </c>
       <c r="H229" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I229" t="n">
         <v>27145</v>
       </c>
       <c r="J229" t="n">
-        <v>0.0300595722294985</v>
+        <v>0.0242780516958002</v>
       </c>
       <c r="K229" t="n">
-        <v>0.0196314268076556</v>
+        <v>0.0150255368581569</v>
       </c>
       <c r="L229" t="n">
-        <v>0.0440604863561774</v>
+        <v>0.0371241560836301</v>
       </c>
       <c r="M229" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="N229" t="n">
-        <v>0.206299502670842</v>
+        <v>0.117885430097624</v>
       </c>
       <c r="O229" t="b">
         <v>0</v>
@@ -12523,10 +12523,10 @@
         <v>0.0285345552384346</v>
       </c>
       <c r="M237" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N237" t="n">
-        <v>0.115406809001731</v>
+        <v>0.0989201220014838</v>
       </c>
       <c r="O237" t="b">
         <v>0</v>
@@ -12558,19 +12558,19 @@
         <v>1</v>
       </c>
       <c r="H238" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I238" t="n">
         <v>32310</v>
       </c>
       <c r="J238" t="n">
-        <v>0.0318492956016163</v>
+        <v>0.023273958982476</v>
       </c>
       <c r="K238" t="n">
-        <v>0.0208027011100107</v>
+        <v>0.0140112024164726</v>
       </c>
       <c r="L238" t="n">
-        <v>0.0466754122372648</v>
+        <v>0.0363512363265144</v>
       </c>
       <c r="M238" t="n">
         <v>60</v>
@@ -12673,10 +12673,10 @@
         <v>0.0181490643352089</v>
       </c>
       <c r="M240" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N240" t="n">
-        <v>0.114342885728579</v>
+        <v>0.100050025012506</v>
       </c>
       <c r="O240" t="b">
         <v>0</v>
@@ -12708,19 +12708,19 @@
         <v>1</v>
       </c>
       <c r="H241" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I241" t="n">
         <v>29769</v>
       </c>
       <c r="J241" t="n">
-        <v>0.0157482859536498</v>
+        <v>0.00833682518753592</v>
       </c>
       <c r="K241" t="n">
-        <v>0.00917202346831251</v>
+        <v>0.00381163784811002</v>
       </c>
       <c r="L241" t="n">
-        <v>0.025224191246831</v>
+        <v>0.0158307053651237</v>
       </c>
       <c r="M241" t="n">
         <v>56</v>
@@ -12773,10 +12773,10 @@
         <v>0.0175636231781437</v>
       </c>
       <c r="M242" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N242" t="n">
-        <v>0.124524839428497</v>
+        <v>0.117970900511207</v>
       </c>
       <c r="O242" t="b">
         <v>0</v>
@@ -12823,10 +12823,10 @@
         <v>0.0157044971918804</v>
       </c>
       <c r="M243" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N243" t="n">
-        <v>0.118334442718734</v>
+        <v>0.103542637378892</v>
       </c>
       <c r="O243" t="b">
         <v>0</v>
@@ -12858,19 +12858,19 @@
         <v>1</v>
       </c>
       <c r="H244" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I244" t="n">
         <v>30686</v>
       </c>
       <c r="J244" t="n">
-        <v>0.0323390908462578</v>
+        <v>0.0281656435774004</v>
       </c>
       <c r="K244" t="n">
-        <v>0.0219680844287211</v>
+        <v>0.0185576723626286</v>
       </c>
       <c r="L244" t="n">
-        <v>0.045918166742278</v>
+        <v>0.0409925348551718</v>
       </c>
       <c r="M244" t="n">
         <v>57</v>
@@ -12958,25 +12958,25 @@
         <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I246" t="n">
         <v>12541</v>
       </c>
       <c r="J246" t="n">
-        <v>0.0224647614213972</v>
+        <v>0.00371423890477046</v>
       </c>
       <c r="K246" t="n">
-        <v>0.0132608700525714</v>
+        <v>0.000765376236545985</v>
       </c>
       <c r="L246" t="n">
-        <v>0.0357126738406201</v>
+        <v>0.0108914568492566</v>
       </c>
       <c r="M246" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="N246" t="n">
-        <v>0.207319990431385</v>
+        <v>0.111633841001515</v>
       </c>
       <c r="O246" t="b">
         <v>0</v>
@@ -13073,10 +13073,10 @@
         <v>0.0274987554911442</v>
       </c>
       <c r="M248" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N248" t="n">
-        <v>0.124185035703198</v>
+        <v>0.117975783918038</v>
       </c>
       <c r="O248" t="b">
         <v>0</v>
@@ -13123,10 +13123,10 @@
         <v>0.0585564719758217</v>
       </c>
       <c r="M249" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N249" t="n">
-        <v>0.119741358665283</v>
+        <v>0.103775844176579</v>
       </c>
       <c r="O249" t="b">
         <v>0</v>
@@ -13158,19 +13158,19 @@
         <v>1</v>
       </c>
       <c r="H250" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I250" t="n">
         <v>30037</v>
       </c>
       <c r="J250" t="n">
-        <v>0.0423080545305024</v>
+        <v>0.0335965824801844</v>
       </c>
       <c r="K250" t="n">
-        <v>0.0292947231718205</v>
+        <v>0.022137236648273</v>
       </c>
       <c r="L250" t="n">
-        <v>0.0591363918304523</v>
+        <v>0.0488926439835844</v>
       </c>
       <c r="M250" t="n">
         <v>56</v>
@@ -13223,10 +13223,10 @@
         <v>0.112223546186696</v>
       </c>
       <c r="M251" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N251" t="n">
-        <v>0.134722471708281</v>
+        <v>0.125740973594396</v>
       </c>
       <c r="O251" t="b">
         <v>0</v>
@@ -13273,10 +13273,10 @@
         <v>0.0258888550888256</v>
       </c>
       <c r="M252" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N252" t="n">
-        <v>0.118965004461188</v>
+        <v>0.109051254089422</v>
       </c>
       <c r="O252" t="b">
         <v>0</v>
@@ -13458,19 +13458,19 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I256" t="n">
         <v>14695</v>
       </c>
       <c r="J256" t="n">
-        <v>0.00733145626922104</v>
+        <v>0.00122177612372312</v>
       </c>
       <c r="K256" t="n">
-        <v>0.00268857985488806</v>
+        <v>0.0000309309933817933</v>
       </c>
       <c r="L256" t="n">
-        <v>0.0159885163407004</v>
+        <v>0.00681602419389533</v>
       </c>
       <c r="M256" t="n">
         <v>7</v>
@@ -13908,19 +13908,19 @@
         <v>0</v>
       </c>
       <c r="H265" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I265" t="n">
         <v>14618</v>
       </c>
       <c r="J265" t="n">
-        <v>0.0432147699885498</v>
+        <v>0.0265935755099208</v>
       </c>
       <c r="K265" t="n">
-        <v>0.0230082021317209</v>
+        <v>0.0114806611531036</v>
       </c>
       <c r="L265" t="n">
-        <v>0.0739134899875818</v>
+        <v>0.0524089013941601</v>
       </c>
       <c r="M265" t="n">
         <v>7</v>
@@ -14058,19 +14058,19 @@
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I268" t="n">
         <v>13465</v>
       </c>
       <c r="J268" t="n">
-        <v>0.0284819287247281</v>
+        <v>0.0213589982176252</v>
       </c>
       <c r="K268" t="n">
-        <v>0.017369311978727</v>
+        <v>0.0119387294577044</v>
       </c>
       <c r="L268" t="n">
-        <v>0.0441008030144881</v>
+        <v>0.0353093165181707</v>
       </c>
       <c r="M268" t="n">
         <v>7</v>
@@ -14123,10 +14123,10 @@
         <v>0.023170510100858</v>
       </c>
       <c r="M269" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N269" t="n">
-        <v>0.126342387871131</v>
+        <v>0.119323366322735</v>
       </c>
       <c r="O269" t="b">
         <v>0</v>
@@ -14173,10 +14173,10 @@
         <v>0.039475269172782</v>
       </c>
       <c r="M270" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N270" t="n">
-        <v>0.118231260345235</v>
+        <v>0.102467092299204</v>
       </c>
       <c r="O270" t="b">
         <v>0</v>
@@ -14208,19 +14208,19 @@
         <v>0</v>
       </c>
       <c r="H271" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I271" t="n">
         <v>15022</v>
       </c>
       <c r="J271" t="n">
-        <v>0.0209987346152632</v>
+        <v>0.0163320237628352</v>
       </c>
       <c r="K271" t="n">
-        <v>0.00960057953273899</v>
+        <v>0.00656556766656334</v>
       </c>
       <c r="L271" t="n">
-        <v>0.0398762082399627</v>
+        <v>0.0336611412556119</v>
       </c>
       <c r="M271" t="n">
         <v>8</v>
@@ -14229,7 +14229,7 @@
         <v>0.0532552256690188</v>
       </c>
       <c r="O271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P271" t="b">
         <v>0</v>
@@ -14273,10 +14273,10 @@
         <v>0.0180421879892845</v>
       </c>
       <c r="M272" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N272" t="n">
-        <v>0.1284315299406</v>
+        <v>0.120404559319313</v>
       </c>
       <c r="O272" t="b">
         <v>0</v>
@@ -14323,10 +14323,10 @@
         <v>0.0157835464883712</v>
       </c>
       <c r="M273" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N273" t="n">
-        <v>0.113938473224459</v>
+        <v>0.0987466767945309</v>
       </c>
       <c r="O273" t="b">
         <v>0</v>
@@ -14358,19 +14358,19 @@
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I274" t="n">
         <v>12075</v>
       </c>
       <c r="J274" t="n">
-        <v>0.00914845453432767</v>
+        <v>0.00228698641314261</v>
       </c>
       <c r="K274" t="n">
-        <v>0.00249227210603446</v>
+        <v>0.0000578996723631444</v>
       </c>
       <c r="L274" t="n">
-        <v>0.0234372784732292</v>
+        <v>0.0127477872643623</v>
       </c>
       <c r="M274" t="n">
         <v>6</v>
@@ -14558,25 +14558,25 @@
         <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I278" t="n">
         <v>14119</v>
       </c>
       <c r="J278" t="n">
-        <v>0.0287694042278289</v>
+        <v>0.0104609227901367</v>
       </c>
       <c r="K278" t="n">
-        <v>0.0143592920660324</v>
+        <v>0.00285007803213279</v>
       </c>
       <c r="L278" t="n">
-        <v>0.0514949707337671</v>
+        <v>0.0267911398266989</v>
       </c>
       <c r="M278" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="N278" t="n">
-        <v>0.134570436999788</v>
+        <v>0.0495785820525533</v>
       </c>
       <c r="O278" t="b">
         <v>0</v>
@@ -14608,25 +14608,25 @@
         <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I279" t="n">
         <v>14930</v>
       </c>
       <c r="J279" t="n">
-        <v>0.070504861935171</v>
+        <v>0.0388945806719051</v>
       </c>
       <c r="K279" t="n">
-        <v>0.0472029102748649</v>
+        <v>0.0222269098083999</v>
       </c>
       <c r="L279" t="n">
-        <v>0.101308599404587</v>
+        <v>0.063187979012589</v>
       </c>
       <c r="M279" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N279" t="n">
-        <v>0.167448091091762</v>
+        <v>0.100468854655057</v>
       </c>
       <c r="O279" t="b">
         <v>1</v>
@@ -14658,28 +14658,28 @@
         <v>0</v>
       </c>
       <c r="H280" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I280" t="n">
         <v>15533</v>
       </c>
       <c r="J280" t="n">
-        <v>0.0670178592357547</v>
+        <v>0.0502604816861352</v>
       </c>
       <c r="K280" t="n">
-        <v>0.0445200816626616</v>
+        <v>0.0311047281900283</v>
       </c>
       <c r="L280" t="n">
-        <v>0.0969041526233785</v>
+        <v>0.0768600936563661</v>
       </c>
       <c r="M280" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N280" t="n">
-        <v>0.218888817356596</v>
+        <v>0.128758127856821</v>
       </c>
       <c r="O280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P280" t="b">
         <v>0</v>
@@ -14723,10 +14723,10 @@
         <v>0.0312896121744421</v>
       </c>
       <c r="M281" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N281" t="n">
-        <v>0.131937000082461</v>
+        <v>0.123690937577307</v>
       </c>
       <c r="O281" t="b">
         <v>0</v>
@@ -14808,19 +14808,19 @@
         <v>0</v>
       </c>
       <c r="H283" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I283" t="n">
         <v>14478</v>
       </c>
       <c r="J283" t="n">
-        <v>0.0194894155556128</v>
+        <v>0.0129915429990885</v>
       </c>
       <c r="K283" t="n">
-        <v>0.0108937754269527</v>
+        <v>0.00622399607687319</v>
       </c>
       <c r="L283" t="n">
-        <v>0.032218266447252</v>
+        <v>0.0239390281538801</v>
       </c>
       <c r="M283" t="n">
         <v>7</v>
@@ -14923,10 +14923,10 @@
         <v>0.02516111023792</v>
       </c>
       <c r="M285" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N285" t="n">
-        <v>0.120695204377213</v>
+        <v>0.104602510460251</v>
       </c>
       <c r="O285" t="b">
         <v>0</v>
@@ -15023,10 +15023,10 @@
         <v>0.0352662913381714</v>
       </c>
       <c r="M287" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N287" t="n">
-        <v>0.125823403152986</v>
+        <v>0.118422026496928</v>
       </c>
       <c r="O287" t="b">
         <v>0</v>
@@ -15073,10 +15073,10 @@
         <v>0.0420348170760134</v>
       </c>
       <c r="M288" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N288" t="n">
-        <v>0.121862052156958</v>
+        <v>0.105613778536031</v>
       </c>
       <c r="O288" t="b">
         <v>0</v>
@@ -15108,19 +15108,19 @@
         <v>0</v>
       </c>
       <c r="H289" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I289" t="n">
         <v>13811</v>
       </c>
       <c r="J289" t="n">
-        <v>0.0128947432252764</v>
+        <v>0.00736803144000712</v>
       </c>
       <c r="K289" t="n">
-        <v>0.00518289956060794</v>
+        <v>0.00200721562038107</v>
       </c>
       <c r="L289" t="n">
-        <v>0.0265876579681013</v>
+        <v>0.0188768250511496</v>
       </c>
       <c r="M289" t="n">
         <v>7</v>
@@ -15223,10 +15223,10 @@
         <v>0.0366602215738631</v>
       </c>
       <c r="M291" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N291" t="n">
-        <v>0.12271946330688</v>
+        <v>0.106356868199296</v>
       </c>
       <c r="O291" t="b">
         <v>0</v>
@@ -15323,10 +15323,10 @@
         <v>0.0723854955259818</v>
       </c>
       <c r="M293" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N293" t="n">
-        <v>0.132702994111305</v>
+        <v>0.124409056979348</v>
       </c>
       <c r="O293" t="b">
         <v>0</v>
@@ -15473,10 +15473,10 @@
         <v>0.0556467609877703</v>
       </c>
       <c r="M296" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N296" t="n">
-        <v>0.127235985330439</v>
+        <v>0.119751515605119</v>
       </c>
       <c r="O296" t="b">
         <v>0</v>
@@ -15523,10 +15523,10 @@
         <v>0.0231906518093525</v>
       </c>
       <c r="M297" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N297" t="n">
-        <v>0.118229513042193</v>
+        <v>0.103450823911919</v>
       </c>
       <c r="O297" t="b">
         <v>0</v>
@@ -15623,10 +15623,10 @@
         <v>0.0515802787637369</v>
       </c>
       <c r="M299" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N299" t="n">
-        <v>0.129248080285866</v>
+        <v>0.121645252033757</v>
       </c>
       <c r="O299" t="b">
         <v>0</v>
@@ -15673,10 +15673,10 @@
         <v>0.0416781170232105</v>
       </c>
       <c r="M300" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N300" t="n">
-        <v>0.11858000444675</v>
+        <v>0.103757503890906</v>
       </c>
       <c r="O300" t="b">
         <v>0</v>
@@ -15708,19 +15708,19 @@
         <v>1</v>
       </c>
       <c r="H301" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I301" t="n">
         <v>28232</v>
       </c>
       <c r="J301" t="n">
-        <v>0.0198633396764478</v>
+        <v>0.0132414609780904</v>
       </c>
       <c r="K301" t="n">
-        <v>0.0122922690211554</v>
+        <v>0.00723771577110963</v>
       </c>
       <c r="L301" t="n">
-        <v>0.0303776227740523</v>
+        <v>0.0222259437102681</v>
       </c>
       <c r="M301" t="n">
         <v>53</v>
@@ -15773,10 +15773,10 @@
         <v>0.0282236923226029</v>
       </c>
       <c r="M302" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N302" t="n">
-        <v>0.127979523276276</v>
+        <v>0.119980803071509</v>
       </c>
       <c r="O302" t="b">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0.0114347000556112</v>
       </c>
       <c r="M303" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N303" t="n">
-        <v>0.116567098936325</v>
+        <v>0.101996211569285</v>
       </c>
       <c r="O303" t="b">
         <v>0</v>
@@ -15858,19 +15858,19 @@
         <v>1</v>
       </c>
       <c r="H304" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I304" t="n">
         <v>27904</v>
       </c>
       <c r="J304" t="n">
-        <v>0.00700804692217495</v>
+        <v>0.00300335366509549</v>
       </c>
       <c r="K304" t="n">
-        <v>0.00281729769734806</v>
+        <v>0.000619336115466423</v>
       </c>
       <c r="L304" t="n">
-        <v>0.0144434337388966</v>
+        <v>0.00877906477039837</v>
       </c>
       <c r="M304" t="n">
         <v>53</v>
@@ -15973,10 +15973,10 @@
         <v>0.0370378102646554</v>
       </c>
       <c r="M306" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N306" t="n">
-        <v>0.11955049015701</v>
+        <v>0.103610424802742</v>
       </c>
       <c r="O306" t="b">
         <v>0</v>
@@ -16008,19 +16008,19 @@
         <v>1</v>
       </c>
       <c r="H307" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I307" t="n">
         <v>29455</v>
       </c>
       <c r="J307" t="n">
-        <v>0.0374269153457176</v>
+        <v>0.0277672659326482</v>
       </c>
       <c r="K307" t="n">
-        <v>0.0254252621676855</v>
+        <v>0.0175995222997445</v>
       </c>
       <c r="L307" t="n">
-        <v>0.0531393402194622</v>
+        <v>0.0416748366088401</v>
       </c>
       <c r="M307" t="n">
         <v>55</v>
@@ -16058,19 +16058,19 @@
         <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I308" t="n">
         <v>30392</v>
       </c>
       <c r="J308" t="n">
-        <v>0.0103925082175805</v>
+        <v>0.00296901989487178</v>
       </c>
       <c r="K308" t="n">
-        <v>0.0056799221692735</v>
+        <v>0.000808876642920184</v>
       </c>
       <c r="L308" t="n">
-        <v>0.0174471776774006</v>
+        <v>0.00760485431737237</v>
       </c>
       <c r="M308" t="n">
         <v>40</v>
@@ -16108,25 +16108,25 @@
         <v>1</v>
       </c>
       <c r="H309" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I309" t="n">
         <v>31198</v>
       </c>
       <c r="J309" t="n">
-        <v>0.0100268829398029</v>
+        <v>0.006445567503649</v>
       </c>
       <c r="K309" t="n">
-        <v>0.00548008951094989</v>
+        <v>0.00294668021026893</v>
       </c>
       <c r="L309" t="n">
-        <v>0.0168333772001325</v>
+        <v>0.0122418882519083</v>
       </c>
       <c r="M309" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="N309" t="n">
-        <v>0.153856016411308</v>
+        <v>0.0929546765818322</v>
       </c>
       <c r="O309" t="b">
         <v>0</v>
@@ -16158,19 +16158,19 @@
         <v>1</v>
       </c>
       <c r="H310" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I310" t="n">
         <v>27270</v>
       </c>
       <c r="J310" t="n">
-        <v>0.0345437217847463</v>
+        <v>0.0333920362920311</v>
       </c>
       <c r="K310" t="n">
-        <v>0.0233006784945996</v>
+        <v>0.0223577060634165</v>
       </c>
       <c r="L310" t="n">
-        <v>0.0493324822233669</v>
+        <v>0.0479749215825437</v>
       </c>
       <c r="M310" t="n">
         <v>108</v>
@@ -16273,10 +16273,10 @@
         <v>0.0705123253394388</v>
       </c>
       <c r="M312" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N312" t="n">
-        <v>0.119569549621363</v>
+        <v>0.103626943005181</v>
       </c>
       <c r="O312" t="b">
         <v>0</v>
@@ -16458,19 +16458,19 @@
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I316" t="n">
         <v>12727</v>
       </c>
       <c r="J316" t="n">
-        <v>0.00591785754471173</v>
+        <v>0</v>
       </c>
       <c r="K316" t="n">
-        <v>0.00122024393404796</v>
+        <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>0.0173056895568469</v>
+        <v>0.00727944151215941</v>
       </c>
       <c r="M316" t="n">
         <v>7</v>
@@ -16508,25 +16508,25 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I317" t="n">
         <v>15846</v>
       </c>
       <c r="J317" t="n">
-        <v>0.01697860455006</v>
+        <v>0.00565874639312321</v>
       </c>
       <c r="K317" t="n">
-        <v>0.00876826824283698</v>
+        <v>0.00154150813839724</v>
       </c>
       <c r="L317" t="n">
-        <v>0.0296905725467795</v>
+        <v>0.0144997420776511</v>
       </c>
       <c r="M317" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N317" t="n">
-        <v>0.126214817619589</v>
+        <v>0.0504859270478354</v>
       </c>
       <c r="O317" t="b">
         <v>0</v>
@@ -16558,25 +16558,25 @@
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I318" t="n">
         <v>15668</v>
       </c>
       <c r="J318" t="n">
-        <v>0.0234493863934524</v>
+        <v>0.0131886851316403</v>
       </c>
       <c r="K318" t="n">
-        <v>0.013394728410068</v>
+        <v>0.00602823274465662</v>
       </c>
       <c r="L318" t="n">
-        <v>0.0381239829663104</v>
+        <v>0.0250595462898831</v>
       </c>
       <c r="M318" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N318" t="n">
-        <v>0.165943323972428</v>
+        <v>0.102118968598417</v>
       </c>
       <c r="O318" t="b">
         <v>0</v>
@@ -16908,19 +16908,19 @@
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I325" t="n">
         <v>11701</v>
       </c>
       <c r="J325" t="n">
-        <v>0.0124304190086114</v>
+        <v>0.00966754410260298</v>
       </c>
       <c r="K325" t="n">
-        <v>0.0056718172677487</v>
+        <v>0.00388019062182592</v>
       </c>
       <c r="L325" t="n">
-        <v>0.0236970741125461</v>
+        <v>0.0199966671439778</v>
       </c>
       <c r="M325" t="n">
         <v>6</v>
@@ -16958,25 +16958,25 @@
         <v>0</v>
       </c>
       <c r="H326" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I326" t="n">
         <v>13928</v>
       </c>
       <c r="J326" t="n">
-        <v>0.0333690165848397</v>
+        <v>0.0111214853485475</v>
       </c>
       <c r="K326" t="n">
-        <v>0.0186705031226506</v>
+        <v>0.00361067523731191</v>
       </c>
       <c r="L326" t="n">
-        <v>0.0550699519040177</v>
+        <v>0.0259645330164218</v>
       </c>
       <c r="M326" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N326" t="n">
-        <v>0.129236071223435</v>
+        <v>0.0502584721424469</v>
       </c>
       <c r="O326" t="b">
         <v>0</v>
@@ -17008,25 +17008,25 @@
         <v>0</v>
       </c>
       <c r="H327" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I327" t="n">
         <v>16119</v>
       </c>
       <c r="J327" t="n">
-        <v>0.0189160739769084</v>
+        <v>0.00630497938794801</v>
       </c>
       <c r="K327" t="n">
-        <v>0.00864837764037597</v>
+        <v>0.00130017608914555</v>
       </c>
       <c r="L327" t="n">
-        <v>0.0359212976446775</v>
+        <v>0.0184305323225313</v>
       </c>
       <c r="M327" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="N327" t="n">
-        <v>0.16750418760469</v>
+        <v>0.0992617408027793</v>
       </c>
       <c r="O327" t="b">
         <v>0</v>
@@ -17058,25 +17058,25 @@
         <v>0</v>
       </c>
       <c r="H328" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I328" t="n">
         <v>15538</v>
       </c>
       <c r="J328" t="n">
-        <v>0.0273881285404488</v>
+        <v>0.0231740547120476</v>
       </c>
       <c r="K328" t="n">
-        <v>0.0145797985937755</v>
+        <v>0.0115661635815478</v>
       </c>
       <c r="L328" t="n">
-        <v>0.0468555930770103</v>
+        <v>0.0414823426523948</v>
       </c>
       <c r="M328" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N328" t="n">
-        <v>0.218818380743982</v>
+        <v>0.128716694555284</v>
       </c>
       <c r="O328" t="b">
         <v>0</v>
@@ -17208,19 +17208,19 @@
         <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I331" t="n">
         <v>14062</v>
       </c>
       <c r="J331" t="n">
-        <v>0.00544927930100258</v>
+        <v>0.00272452010253152</v>
       </c>
       <c r="K331" t="n">
-        <v>0.00148417461051809</v>
+        <v>0.000329901016174722</v>
       </c>
       <c r="L331" t="n">
-        <v>0.013972199360752</v>
+        <v>0.00985372516403597</v>
       </c>
       <c r="M331" t="n">
         <v>7</v>
@@ -17358,19 +17358,19 @@
         <v>0</v>
       </c>
       <c r="H334" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I334" t="n">
         <v>13632</v>
       </c>
       <c r="J334" t="n">
-        <v>0.0172124339087792</v>
+        <v>0.00172094170558846</v>
       </c>
       <c r="K334" t="n">
-        <v>0.00825002670363795</v>
+        <v>0.0000435689425918128</v>
       </c>
       <c r="L334" t="n">
-        <v>0.0316873293923899</v>
+        <v>0.00959405643995288</v>
       </c>
       <c r="M334" t="n">
         <v>7</v>
@@ -17379,7 +17379,7 @@
         <v>0.051349765258216</v>
       </c>
       <c r="O334" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P334" t="b">
         <v>0</v>
@@ -17408,25 +17408,25 @@
         <v>0</v>
       </c>
       <c r="H335" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I335" t="n">
         <v>15997</v>
       </c>
       <c r="J335" t="n">
-        <v>0.0215168450862975</v>
+        <v>0.00268893470206019</v>
       </c>
       <c r="K335" t="n">
-        <v>0.012289254802382</v>
+        <v>0.000325611949309817</v>
       </c>
       <c r="L335" t="n">
-        <v>0.0349895562213661</v>
+        <v>0.00972039177568561</v>
       </c>
       <c r="M335" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="N335" t="n">
-        <v>0.131274613990123</v>
+        <v>0.0500093767581422</v>
       </c>
       <c r="O335" t="b">
         <v>0</v>
@@ -17458,25 +17458,25 @@
         <v>0</v>
       </c>
       <c r="H336" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I336" t="n">
         <v>15255</v>
       </c>
       <c r="J336" t="n">
-        <v>0.0199554875722225</v>
+        <v>0.00460430957446635</v>
       </c>
       <c r="K336" t="n">
-        <v>0.0106197808816052</v>
+        <v>0.000949393922766764</v>
       </c>
       <c r="L336" t="n">
-        <v>0.0341596713645852</v>
+        <v>0.0134645169802893</v>
       </c>
       <c r="M336" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N336" t="n">
-        <v>0.170435922648312</v>
+        <v>0.104883644706654</v>
       </c>
       <c r="O336" t="b">
         <v>0</v>
@@ -17508,25 +17508,25 @@
         <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I337" t="n">
         <v>15779</v>
       </c>
       <c r="J337" t="n">
-        <v>0.0376092048105642</v>
+        <v>0.028927163197138</v>
       </c>
       <c r="K337" t="n">
-        <v>0.0245451279715569</v>
+        <v>0.0176559734247611</v>
       </c>
       <c r="L337" t="n">
-        <v>0.0551834023869517</v>
+        <v>0.0447320565318084</v>
       </c>
       <c r="M337" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N337" t="n">
-        <v>0.215476265923062</v>
+        <v>0.126750744660625</v>
       </c>
       <c r="O337" t="b">
         <v>0</v>
@@ -17558,28 +17558,28 @@
         <v>0</v>
       </c>
       <c r="H338" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I338" t="n">
         <v>15868</v>
       </c>
       <c r="J338" t="n">
-        <v>0.0329171179798099</v>
+        <v>0.0174250141245123</v>
       </c>
       <c r="K338" t="n">
-        <v>0.0191695218972579</v>
+        <v>0.00796633454637877</v>
       </c>
       <c r="L338" t="n">
-        <v>0.0527329807517745</v>
+        <v>0.0330928066870565</v>
       </c>
       <c r="M338" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="N338" t="n">
-        <v>0.132341820015125</v>
+        <v>0.0504159314343332</v>
       </c>
       <c r="O338" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P338" t="b">
         <v>0</v>
@@ -17608,25 +17608,25 @@
         <v>0</v>
       </c>
       <c r="H339" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I339" t="n">
         <v>17084</v>
       </c>
       <c r="J339" t="n">
-        <v>0.0296840705877736</v>
+        <v>0.0166960360436658</v>
       </c>
       <c r="K339" t="n">
-        <v>0.0169627045779617</v>
+        <v>0.00763326275180682</v>
       </c>
       <c r="L339" t="n">
-        <v>0.0482279235444857</v>
+        <v>0.0317064926228116</v>
       </c>
       <c r="M339" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="N339" t="n">
-        <v>0.163896043081246</v>
+        <v>0.0995083118707563</v>
       </c>
       <c r="O339" t="b">
         <v>0</v>
@@ -17658,25 +17658,25 @@
         <v>0</v>
       </c>
       <c r="H340" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I340" t="n">
         <v>14560</v>
       </c>
       <c r="J340" t="n">
-        <v>0.0471198350377306</v>
+        <v>0.0235565631000295</v>
       </c>
       <c r="K340" t="n">
-        <v>0.0295182039805557</v>
+        <v>0.0117566133420884</v>
       </c>
       <c r="L340" t="n">
-        <v>0.0713865090324515</v>
+        <v>0.0421703815540035</v>
       </c>
       <c r="M340" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="N340" t="n">
-        <v>0.21978021978022</v>
+        <v>0.130494505494506</v>
       </c>
       <c r="O340" t="b">
         <v>0</v>
@@ -17808,19 +17808,19 @@
         <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I343" t="n">
         <v>13268</v>
       </c>
       <c r="J343" t="n">
-        <v>0.0122707160976492</v>
+        <v>0.00876444372396332</v>
       </c>
       <c r="K343" t="n">
-        <v>0.00493160315848548</v>
+        <v>0.00284501162581199</v>
       </c>
       <c r="L343" t="n">
-        <v>0.0253070118269587</v>
+        <v>0.0204712508075582</v>
       </c>
       <c r="M343" t="n">
         <v>7</v>
@@ -17958,19 +17958,19 @@
         <v>1</v>
       </c>
       <c r="H346" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I346" t="n">
         <v>31703</v>
       </c>
       <c r="J346" t="n">
-        <v>0.00484341842756426</v>
+        <v>0.00276759415923928</v>
       </c>
       <c r="K346" t="n">
-        <v>0.00194694982766097</v>
+        <v>0.00075399729881355</v>
       </c>
       <c r="L346" t="n">
-        <v>0.00998412022945895</v>
+        <v>0.00708903620798483</v>
       </c>
       <c r="M346" t="n">
         <v>49</v>
@@ -18108,19 +18108,19 @@
         <v>1</v>
       </c>
       <c r="H349" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I349" t="n">
         <v>31611</v>
       </c>
       <c r="J349" t="n">
-        <v>0.00155002106349629</v>
+        <v>0.000774992019541346</v>
       </c>
       <c r="K349" t="n">
-        <v>0.000421603012062184</v>
+        <v>0.0000937949697398922</v>
       </c>
       <c r="L349" t="n">
-        <v>0.00398875454288653</v>
+        <v>0.00281147341717459</v>
       </c>
       <c r="M349" t="n">
         <v>48</v>
@@ -18308,25 +18308,25 @@
         <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I353" t="n">
         <v>15677</v>
       </c>
       <c r="J353" t="n">
-        <v>0.0183899983329175</v>
+        <v>0.00108139963532508</v>
       </c>
       <c r="K353" t="n">
-        <v>0.0106910461802925</v>
+        <v>0.000027377017473748</v>
       </c>
       <c r="L353" t="n">
-        <v>0.0295407793611212</v>
+        <v>0.0060342271449979</v>
       </c>
       <c r="M353" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N353" t="n">
-        <v>0.12757542897238</v>
+        <v>0.051030171588952</v>
       </c>
       <c r="O353" t="b">
         <v>0</v>
@@ -18358,25 +18358,25 @@
         <v>0</v>
       </c>
       <c r="H354" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I354" t="n">
         <v>16354</v>
       </c>
       <c r="J354" t="n">
-        <v>0.0258686253540948</v>
+        <v>0.00822860124023467</v>
       </c>
       <c r="K354" t="n">
-        <v>0.0161891169861627</v>
+        <v>0.00330644482724072</v>
       </c>
       <c r="L354" t="n">
-        <v>0.0392504484856581</v>
+        <v>0.0169783706248495</v>
       </c>
       <c r="M354" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N354" t="n">
-        <v>0.165097223920753</v>
+        <v>0.103950103950104</v>
       </c>
       <c r="O354" t="b">
         <v>0</v>
@@ -18408,25 +18408,25 @@
         <v>0</v>
       </c>
       <c r="H355" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I355" t="n">
         <v>15242</v>
       </c>
       <c r="J355" t="n">
-        <v>0.0310557510084371</v>
+        <v>0.0229515887454067</v>
       </c>
       <c r="K355" t="n">
-        <v>0.0196627614892188</v>
+        <v>0.0133570123447606</v>
       </c>
       <c r="L355" t="n">
-        <v>0.0466869351670507</v>
+        <v>0.0368094397448116</v>
       </c>
       <c r="M355" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="N355" t="n">
-        <v>0.216507020076106</v>
+        <v>0.124655557013515</v>
       </c>
       <c r="O355" t="b">
         <v>0</v>
@@ -18458,25 +18458,25 @@
         <v>0</v>
       </c>
       <c r="H356" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I356" t="n">
         <v>14269</v>
       </c>
       <c r="J356" t="n">
-        <v>0.0225763534740198</v>
+        <v>0.00347260946163277</v>
       </c>
       <c r="K356" t="n">
-        <v>0.0120150999840845</v>
+        <v>0.000420518794667173</v>
       </c>
       <c r="L356" t="n">
-        <v>0.0386427486176113</v>
+        <v>0.0125510867409909</v>
       </c>
       <c r="M356" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N356" t="n">
-        <v>0.133155792276964</v>
+        <v>0.0560655967481954</v>
       </c>
       <c r="O356" t="b">
         <v>0</v>
@@ -18508,25 +18508,25 @@
         <v>0</v>
       </c>
       <c r="H357" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I357" t="n">
         <v>14955</v>
       </c>
       <c r="J357" t="n">
-        <v>0.0115416555622724</v>
+        <v>0.00659489632772097</v>
       </c>
       <c r="K357" t="n">
-        <v>0.00463903646143343</v>
+        <v>0.00179659565809899</v>
       </c>
       <c r="L357" t="n">
-        <v>0.0237977639849356</v>
+        <v>0.0168960810400652</v>
       </c>
       <c r="M357" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N357" t="n">
-        <v>0.167168171180207</v>
+        <v>0.100300902708124</v>
       </c>
       <c r="O357" t="b">
         <v>0</v>
@@ -18658,25 +18658,25 @@
         <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I360" t="n">
         <v>15631</v>
       </c>
       <c r="J360" t="n">
-        <v>0.0119838857902144</v>
+        <v>0.00599134330088642</v>
       </c>
       <c r="K360" t="n">
-        <v>0.00574159527198594</v>
+        <v>0.00194444867566908</v>
       </c>
       <c r="L360" t="n">
-        <v>0.0220796555070007</v>
+        <v>0.0140024995879966</v>
       </c>
       <c r="M360" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N360" t="n">
-        <v>0.16633612692726</v>
+        <v>0.102360693493698</v>
       </c>
       <c r="O360" t="b">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0.0430586168578055</v>
       </c>
       <c r="M362" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N362" t="n">
-        <v>0.136345929100117</v>
+        <v>0.126606934164394</v>
       </c>
       <c r="O362" t="b">
         <v>0</v>
@@ -18823,10 +18823,10 @@
         <v>0.0389218766135965</v>
       </c>
       <c r="M363" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N363" t="n">
-        <v>0.121339589063258</v>
+        <v>0.105160977188157</v>
       </c>
       <c r="O363" t="b">
         <v>0</v>
@@ -18923,10 +18923,10 @@
         <v>0.0565582706433835</v>
       </c>
       <c r="M365" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N365" t="n">
-        <v>0.135750993891205</v>
+        <v>0.126054494327548</v>
       </c>
       <c r="O365" t="b">
         <v>0</v>
@@ -18973,10 +18973,10 @@
         <v>0.0476175038836019</v>
       </c>
       <c r="M366" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N366" t="n">
-        <v>0.115463917525773</v>
+        <v>0.0989690721649484</v>
       </c>
       <c r="O366" t="b">
         <v>0</v>
@@ -19073,10 +19073,10 @@
         <v>0.0563735440157395</v>
       </c>
       <c r="M368" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N368" t="n">
-        <v>0.128174317071217</v>
+        <v>0.120163422254266</v>
       </c>
       <c r="O368" t="b">
         <v>0</v>
@@ -19123,10 +19123,10 @@
         <v>0.0403137701892689</v>
       </c>
       <c r="M369" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N369" t="n">
-        <v>0.115307004900548</v>
+        <v>0.100893629287979</v>
       </c>
       <c r="O369" t="b">
         <v>0</v>
@@ -19223,10 +19223,10 @@
         <v>0.0574015638089767</v>
       </c>
       <c r="M371" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N371" t="n">
-        <v>0.132494203378602</v>
+        <v>0.12421331566744</v>
       </c>
       <c r="O371" t="b">
         <v>0</v>
@@ -19273,10 +19273,10 @@
         <v>0.0434376834193166</v>
       </c>
       <c r="M372" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N372" t="n">
-        <v>0.121538327979859</v>
+        <v>0.104175709697022</v>
       </c>
       <c r="O372" t="b">
         <v>0</v>
@@ -19373,10 +19373,10 @@
         <v>0.054462695541228</v>
       </c>
       <c r="M374" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N374" t="n">
-        <v>0.128845224673861</v>
+        <v>0.120792398131744</v>
       </c>
       <c r="O374" t="b">
         <v>0</v>
@@ -19423,10 +19423,10 @@
         <v>0.0469420772746819</v>
       </c>
       <c r="M375" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N375" t="n">
-        <v>0.12291052114061</v>
+        <v>0.106522451655195</v>
       </c>
       <c r="O375" t="b">
         <v>0</v>
@@ -19573,10 +19573,10 @@
         <v>0.0465209592419369</v>
       </c>
       <c r="M378" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N378" t="n">
-        <v>0.132946579647087</v>
+        <v>0.108774474256708</v>
       </c>
       <c r="O378" t="b">
         <v>0</v>
@@ -19673,10 +19673,10 @@
         <v>0.0932002144417741</v>
       </c>
       <c r="M380" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N380" t="n">
-        <v>0.128803735308324</v>
+        <v>0.120753501851554</v>
       </c>
       <c r="O380" t="b">
         <v>0</v>
@@ -19723,10 +19723,10 @@
         <v>0.0450347114330441</v>
       </c>
       <c r="M381" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N381" t="n">
-        <v>0.117490404950262</v>
+        <v>0.101825017623561</v>
       </c>
       <c r="O381" t="b">
         <v>0</v>
@@ -19758,19 +19758,19 @@
         <v>1</v>
       </c>
       <c r="H382" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I382" t="n">
         <v>28658</v>
       </c>
       <c r="J382" t="n">
-        <v>0.0287294781393898</v>
+        <v>0.0261174778669437</v>
       </c>
       <c r="K382" t="n">
-        <v>0.0180023124660835</v>
+        <v>0.0159513334224855</v>
       </c>
       <c r="L382" t="n">
-        <v>0.0435065278956896</v>
+        <v>0.0403450388959212</v>
       </c>
       <c r="M382" t="n">
         <v>54</v>
@@ -19823,10 +19823,10 @@
         <v>0.0633946848437411</v>
       </c>
       <c r="M383" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N383" t="n">
-        <v>0.128563865991076</v>
+        <v>0.12100128563866</v>
       </c>
       <c r="O383" t="b">
         <v>0</v>
@@ -19873,10 +19873,10 @@
         <v>0.0823908096815058</v>
       </c>
       <c r="M384" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N384" t="n">
-        <v>0.120346598202824</v>
+        <v>0.104300385109114</v>
       </c>
       <c r="O384" t="b">
         <v>0</v>
@@ -19908,19 +19908,19 @@
         <v>1</v>
       </c>
       <c r="H385" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I385" t="n">
         <v>30406</v>
       </c>
       <c r="J385" t="n">
-        <v>0.0424490363280639</v>
+        <v>0.036385299524822</v>
       </c>
       <c r="K385" t="n">
-        <v>0.0262762052754185</v>
+        <v>0.0215639635359016</v>
       </c>
       <c r="L385" t="n">
-        <v>0.0648915532693599</v>
+        <v>0.057507547192276</v>
       </c>
       <c r="M385" t="n">
         <v>57</v>
@@ -19973,10 +19973,10 @@
         <v>0.0537437457968037</v>
       </c>
       <c r="M386" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N386" t="n">
-        <v>0.131708923279552</v>
+        <v>0.12347711557458</v>
       </c>
       <c r="O386" t="b">
         <v>0</v>
@@ -20023,10 +20023,10 @@
         <v>0.0201077019473549</v>
       </c>
       <c r="M387" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N387" t="n">
-        <v>0.126176841696593</v>
+        <v>0.106765019897117</v>
       </c>
       <c r="O387" t="b">
         <v>0</v>
@@ -20058,19 +20058,19 @@
         <v>1</v>
       </c>
       <c r="H388" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I388" t="n">
         <v>28811</v>
       </c>
       <c r="J388" t="n">
-        <v>0.0219792234427738</v>
+        <v>0.0198856898548951</v>
       </c>
       <c r="K388" t="n">
-        <v>0.013602714322761</v>
+        <v>0.0119702126819873</v>
       </c>
       <c r="L388" t="n">
-        <v>0.0336093040417469</v>
+        <v>0.0310643912083968</v>
       </c>
       <c r="M388" t="n">
         <v>54</v>
@@ -20173,10 +20173,10 @@
         <v>0.0163621468962998</v>
       </c>
       <c r="M390" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N390" t="n">
-        <v>0.115321252059308</v>
+        <v>0.0988467874794069</v>
       </c>
       <c r="O390" t="b">
         <v>0</v>
@@ -20208,19 +20208,19 @@
         <v>1</v>
       </c>
       <c r="H391" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I391" t="n">
         <v>26718</v>
       </c>
       <c r="J391" t="n">
-        <v>0.0263816871980245</v>
+        <v>0.0172044501443546</v>
       </c>
       <c r="K391" t="n">
-        <v>0.016719953897812</v>
+        <v>0.00962760363182104</v>
       </c>
       <c r="L391" t="n">
-        <v>0.0396003758836182</v>
+        <v>0.0283851745348466</v>
       </c>
       <c r="M391" t="n">
         <v>51</v>
@@ -20258,25 +20258,25 @@
         <v>0</v>
       </c>
       <c r="H392" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I392" t="n">
         <v>14599</v>
       </c>
       <c r="J392" t="n">
-        <v>0.0193132901349988</v>
+        <v>0.00241341126911944</v>
       </c>
       <c r="K392" t="n">
-        <v>0.0110195966148418</v>
+        <v>0.000292216133464279</v>
       </c>
       <c r="L392" t="n">
-        <v>0.031456342560248</v>
+        <v>0.00873178383435017</v>
       </c>
       <c r="M392" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N392" t="n">
-        <v>0.130145900404137</v>
+        <v>0.0547982738543736</v>
       </c>
       <c r="O392" t="b">
         <v>0</v>
@@ -20308,25 +20308,25 @@
         <v>0</v>
       </c>
       <c r="H393" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I393" t="n">
         <v>13593</v>
       </c>
       <c r="J393" t="n">
-        <v>0.0342423678179727</v>
+        <v>0.016431396935137</v>
       </c>
       <c r="K393" t="n">
-        <v>0.0221134028184727</v>
+        <v>0.00847987815483543</v>
       </c>
       <c r="L393" t="n">
-        <v>0.050704241229183</v>
+        <v>0.0287691407221729</v>
       </c>
       <c r="M393" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="N393" t="n">
-        <v>0.205988376370191</v>
+        <v>0.110350915912602</v>
       </c>
       <c r="O393" t="b">
         <v>0</v>
@@ -20358,28 +20358,28 @@
         <v>0</v>
       </c>
       <c r="H394" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I394" t="n">
         <v>14161</v>
       </c>
       <c r="J394" t="n">
-        <v>0.034234330100018</v>
+        <v>0.0270993217691486</v>
       </c>
       <c r="K394" t="n">
-        <v>0.0219029556388508</v>
+        <v>0.0162955549916638</v>
       </c>
       <c r="L394" t="n">
-        <v>0.0510499293218111</v>
+        <v>0.0424037900210085</v>
       </c>
       <c r="M394" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N394" t="n">
-        <v>0.218911093849304</v>
+        <v>0.12710966739637</v>
       </c>
       <c r="O394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P394" t="b">
         <v>0</v>
@@ -20408,28 +20408,28 @@
         <v>0</v>
       </c>
       <c r="H395" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I395" t="n">
         <v>13924</v>
       </c>
       <c r="J395" t="n">
-        <v>0.0185446094258814</v>
+        <v>0.000926760939924216</v>
       </c>
       <c r="K395" t="n">
-        <v>0.0111844219992757</v>
+        <v>0.000023457829469988</v>
       </c>
       <c r="L395" t="n">
-        <v>0.0290499416894628</v>
+        <v>0.00519530425874429</v>
       </c>
       <c r="M395" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N395" t="n">
-        <v>0.129273197357081</v>
+        <v>0.0502729100833094</v>
       </c>
       <c r="O395" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P395" t="b">
         <v>0</v>
@@ -20458,28 +20458,28 @@
         <v>0</v>
       </c>
       <c r="H396" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="I396" t="n">
         <v>15254</v>
       </c>
       <c r="J396" t="n">
-        <v>0.0395468172790565</v>
+        <v>0.008891710844816</v>
       </c>
       <c r="K396" t="n">
-        <v>0.0280646028947229</v>
+        <v>0.00405653267024507</v>
       </c>
       <c r="L396" t="n">
-        <v>0.0542780129114133</v>
+        <v>0.0169545629995762</v>
       </c>
       <c r="M396" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N396" t="n">
-        <v>0.170447095843713</v>
+        <v>0.104890520519208</v>
       </c>
       <c r="O396" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P396" t="b">
         <v>0</v>
@@ -20508,25 +20508,25 @@
         <v>0</v>
       </c>
       <c r="H397" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I397" t="n">
         <v>15679</v>
       </c>
       <c r="J397" t="n">
-        <v>0.0321354078157856</v>
+        <v>0.0201934262063309</v>
       </c>
       <c r="K397" t="n">
-        <v>0.0222104266343818</v>
+        <v>0.0125828895105316</v>
       </c>
       <c r="L397" t="n">
-        <v>0.0450991019092945</v>
+        <v>0.0308037364815243</v>
       </c>
       <c r="M397" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N397" t="n">
-        <v>0.216850564449263</v>
+        <v>0.12755915555839</v>
       </c>
       <c r="O397" t="b">
         <v>1</v>
@@ -20573,10 +20573,10 @@
         <v>0.0870756405949396</v>
       </c>
       <c r="M398" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N398" t="n">
-        <v>0.129575639779721</v>
+        <v>0.121477162293489</v>
       </c>
       <c r="O398" t="b">
         <v>0</v>
@@ -20623,10 +20623,10 @@
         <v>0.0871697045874413</v>
       </c>
       <c r="M399" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N399" t="n">
-        <v>0.117519435906708</v>
+        <v>0.108479479298499</v>
       </c>
       <c r="O399" t="b">
         <v>0</v>
@@ -20723,10 +20723,10 @@
         <v>0.0501047152868525</v>
       </c>
       <c r="M401" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N401" t="n">
-        <v>0.128400609902897</v>
+        <v>0.120375571783966</v>
       </c>
       <c r="O401" t="b">
         <v>0</v>
@@ -20773,10 +20773,10 @@
         <v>0.0346669668364871</v>
       </c>
       <c r="M402" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N402" t="n">
-        <v>0.115589119210912</v>
+        <v>0.100177236649457</v>
       </c>
       <c r="O402" t="b">
         <v>0</v>
@@ -20873,10 +20873,10 @@
         <v>0.047367602281753</v>
       </c>
       <c r="M404" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N404" t="n">
-        <v>0.127464947139537</v>
+        <v>0.119967009072505</v>
       </c>
       <c r="O404" t="b">
         <v>0</v>
@@ -20923,10 +20923,10 @@
         <v>0.0940611559363081</v>
       </c>
       <c r="M405" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N405" t="n">
-        <v>0.119255843536333</v>
+        <v>0.103355064398156</v>
       </c>
       <c r="O405" t="b">
         <v>0</v>
@@ -21023,10 +21023,10 @@
         <v>0.0566139855181378</v>
       </c>
       <c r="M407" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N407" t="n">
-        <v>0.134746676248653</v>
+        <v>0.125763564498742</v>
       </c>
       <c r="O407" t="b">
         <v>0</v>
@@ -21073,10 +21073,10 @@
         <v>0.0908277658639352</v>
       </c>
       <c r="M408" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N408" t="n">
-        <v>0.124111474669976</v>
+        <v>0.112828613336342</v>
       </c>
       <c r="O408" t="b">
         <v>0</v>
@@ -21223,10 +21223,10 @@
         <v>0.0279766495171053</v>
       </c>
       <c r="M411" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N411" t="n">
-        <v>0.113877922866687</v>
+        <v>0.0986941998177953</v>
       </c>
       <c r="O411" t="b">
         <v>0</v>
@@ -21473,10 +21473,10 @@
         <v>0.0474261277526193</v>
       </c>
       <c r="M416" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N416" t="n">
-        <v>0.129433083096039</v>
+        <v>0.120804210889637</v>
       </c>
       <c r="O416" t="b">
         <v>0</v>
@@ -21523,10 +21523,10 @@
         <v>0.0718408536621055</v>
       </c>
       <c r="M417" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N417" t="n">
-        <v>0.113026278609777</v>
+        <v>0.0988979937835547</v>
       </c>
       <c r="O417" t="b">
         <v>0</v>
@@ -21673,13 +21673,13 @@
         <v>0.133973038988039</v>
       </c>
       <c r="M420" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N420" t="n">
-        <v>0.122936424306287</v>
+        <v>0.105374077976818</v>
       </c>
       <c r="O420" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P420" t="b">
         <v>0</v>
@@ -21823,10 +21823,10 @@
         <v>0.0318281718061333</v>
       </c>
       <c r="M423" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N423" t="n">
-        <v>0.119312758510977</v>
+        <v>0.103404390709513</v>
       </c>
       <c r="O423" t="b">
         <v>0</v>
@@ -22073,10 +22073,10 @@
         <v>0.127185674566487</v>
       </c>
       <c r="M428" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N428" t="n">
-        <v>0.135606354126308</v>
+        <v>0.125920185974429</v>
       </c>
       <c r="O428" t="b">
         <v>0</v>
@@ -22123,10 +22123,10 @@
         <v>0.0594746595237704</v>
       </c>
       <c r="M429" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N429" t="n">
-        <v>0.126076906913217</v>
+        <v>0.105064089094348</v>
       </c>
       <c r="O429" t="b">
         <v>0</v>
@@ -22158,19 +22158,19 @@
         <v>1</v>
       </c>
       <c r="H430" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I430" t="n">
         <v>31582</v>
       </c>
       <c r="J430" t="n">
-        <v>0.0229569758773162</v>
+        <v>0.0197898692055095</v>
       </c>
       <c r="K430" t="n">
-        <v>0.0153689464788073</v>
+        <v>0.0128026605860068</v>
       </c>
       <c r="L430" t="n">
-        <v>0.0329888566536042</v>
+        <v>0.0292294446496603</v>
       </c>
       <c r="M430" t="n">
         <v>59</v>
@@ -22308,19 +22308,19 @@
         <v>1</v>
       </c>
       <c r="H433" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I433" t="n">
         <v>29950</v>
       </c>
       <c r="J433" t="n">
-        <v>0.0269927491343214</v>
+        <v>0.0202442376961343</v>
       </c>
       <c r="K433" t="n">
-        <v>0.0164863166132492</v>
+        <v>0.0113296900500204</v>
       </c>
       <c r="L433" t="n">
-        <v>0.0416954323864654</v>
+        <v>0.0333950464361594</v>
       </c>
       <c r="M433" t="n">
         <v>56</v>
@@ -22373,10 +22373,10 @@
         <v>0.0216268712241299</v>
       </c>
       <c r="M434" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N434" t="n">
-        <v>0.129649137022932</v>
+        <v>0.121546065958998</v>
       </c>
       <c r="O434" t="b">
         <v>0</v>
@@ -22458,19 +22458,19 @@
         <v>1</v>
       </c>
       <c r="H436" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I436" t="n">
         <v>28182</v>
       </c>
       <c r="J436" t="n">
-        <v>0.0168460131910177</v>
+        <v>0.0147403104002538</v>
       </c>
       <c r="K436" t="n">
-        <v>0.00727288694794249</v>
+        <v>0.0059263587624913</v>
       </c>
       <c r="L436" t="n">
-        <v>0.0331950230023201</v>
+        <v>0.0303721317667811</v>
       </c>
       <c r="M436" t="n">
         <v>53</v>
@@ -22573,10 +22573,10 @@
         <v>0.0166824262105218</v>
       </c>
       <c r="M438" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N438" t="n">
-        <v>0.122749590834697</v>
+        <v>0.106382978723404</v>
       </c>
       <c r="O438" t="b">
         <v>0</v>
@@ -22608,19 +22608,19 @@
         <v>1</v>
       </c>
       <c r="H439" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I439" t="n">
         <v>28429</v>
       </c>
       <c r="J439" t="n">
-        <v>0.0216945527542048</v>
+        <v>0.0189822463933321</v>
       </c>
       <c r="K439" t="n">
-        <v>0.0138954139081797</v>
+        <v>0.0117466897284733</v>
       </c>
       <c r="L439" t="n">
-        <v>0.0322974237019963</v>
+        <v>0.0290314262031872</v>
       </c>
       <c r="M439" t="n">
         <v>53</v>
@@ -22723,10 +22723,10 @@
         <v>0.0343605227223589</v>
       </c>
       <c r="M441" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N441" t="n">
-        <v>0.1178390137781</v>
+        <v>0.108774474256708</v>
       </c>
       <c r="O441" t="b">
         <v>0</v>
@@ -22758,19 +22758,19 @@
         <v>1</v>
       </c>
       <c r="H442" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I442" t="n">
         <v>30330</v>
       </c>
       <c r="J442" t="n">
-        <v>0.00951788105901582</v>
+        <v>0.00793156260582412</v>
       </c>
       <c r="K442" t="n">
-        <v>0.00349283586936083</v>
+        <v>0.00257532287669289</v>
       </c>
       <c r="L442" t="n">
-        <v>0.020718020906016</v>
+        <v>0.0185109769283644</v>
       </c>
       <c r="M442" t="n">
         <v>57</v>
@@ -22823,10 +22823,10 @@
         <v>0.0437208424765784</v>
       </c>
       <c r="M443" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N443" t="n">
-        <v>0.132538104705103</v>
+        <v>0.123071097226167</v>
       </c>
       <c r="O443" t="b">
         <v>0</v>
@@ -22873,10 +22873,10 @@
         <v>0.0610065456886325</v>
       </c>
       <c r="M444" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N444" t="n">
-        <v>0.119770724612884</v>
+        <v>0.102660621096758</v>
       </c>
       <c r="O444" t="b">
         <v>0</v>
@@ -22908,19 +22908,19 @@
         <v>1</v>
       </c>
       <c r="H445" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I445" t="n">
         <v>28144</v>
       </c>
       <c r="J445" t="n">
-        <v>0.019518813028169</v>
+        <v>0.0148708462057594</v>
       </c>
       <c r="K445" t="n">
-        <v>0.0120788640056576</v>
+        <v>0.00849789513397838</v>
       </c>
       <c r="L445" t="n">
-        <v>0.0298515189032886</v>
+        <v>0.0241602093108925</v>
       </c>
       <c r="M445" t="n">
         <v>53</v>
@@ -22973,10 +22973,10 @@
         <v>0.0677277285332524</v>
       </c>
       <c r="M446" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N446" t="n">
-        <v>0.129397492923575</v>
+        <v>0.121310149615851</v>
       </c>
       <c r="O446" t="b">
         <v>0</v>
@@ -23023,10 +23023,10 @@
         <v>0.0105891572505972</v>
       </c>
       <c r="M447" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N447" t="n">
-        <v>0.118586449521701</v>
+        <v>0.102774922918808</v>
       </c>
       <c r="O447" t="b">
         <v>0</v>
@@ -23158,25 +23158,25 @@
         <v>0</v>
       </c>
       <c r="H450" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I450" t="n">
         <v>15078</v>
       </c>
       <c r="J450" t="n">
-        <v>0.0407076623627416</v>
+        <v>0.0356186536384159</v>
       </c>
       <c r="K450" t="n">
-        <v>0.0232636845042388</v>
+        <v>0.0194698364513045</v>
       </c>
       <c r="L450" t="n">
-        <v>0.066130311347219</v>
+        <v>0.0597823644052045</v>
       </c>
       <c r="M450" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N450" t="n">
-        <v>0.218861918026263</v>
+        <v>0.205597559358005</v>
       </c>
       <c r="O450" t="b">
         <v>0</v>
@@ -23208,19 +23208,19 @@
         <v>1</v>
       </c>
       <c r="H451" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I451" t="n">
         <v>42567</v>
       </c>
       <c r="J451" t="n">
-        <v>0.0257711784943707</v>
+        <v>0.0227388957626509</v>
       </c>
       <c r="K451" t="n">
-        <v>0.017844398876329</v>
+        <v>0.0153395495694949</v>
       </c>
       <c r="L451" t="n">
-        <v>0.0360215409879077</v>
+        <v>0.03246880811174</v>
       </c>
       <c r="M451" t="n">
         <v>77</v>
@@ -23323,10 +23323,10 @@
         <v>0.0285559013965602</v>
       </c>
       <c r="M453" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N453" t="n">
-        <v>0.120559395595563</v>
+        <v>0.104484809516155</v>
       </c>
       <c r="O453" t="b">
         <v>0</v>
@@ -23423,10 +23423,10 @@
         <v>0.0552722507744152</v>
       </c>
       <c r="M455" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N455" t="n">
-        <v>0.128524986769487</v>
+        <v>0.120964693430105</v>
       </c>
       <c r="O455" t="b">
         <v>0</v>
@@ -23473,10 +23473,10 @@
         <v>0.03098848965064</v>
       </c>
       <c r="M456" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N456" t="n">
-        <v>0.114068441064639</v>
+        <v>0.0988593155893536</v>
       </c>
       <c r="O456" t="b">
         <v>0</v>
@@ -23573,10 +23573,10 @@
         <v>0.0538908498045714</v>
       </c>
       <c r="M458" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N458" t="n">
-        <v>0.126306925829766</v>
+        <v>0.119289874394779</v>
       </c>
       <c r="O458" t="b">
         <v>0</v>
@@ -23623,10 +23623,10 @@
         <v>0.0768061096222524</v>
       </c>
       <c r="M459" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N459" t="n">
-        <v>0.121094696052313</v>
+        <v>0.104948736578671</v>
       </c>
       <c r="O459" t="b">
         <v>0</v>
@@ -23773,10 +23773,10 @@
         <v>0.0286634811152069</v>
       </c>
       <c r="M462" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N462" t="n">
-        <v>0.121292314477892</v>
+        <v>0.110265740434447</v>
       </c>
       <c r="O462" t="b">
         <v>0</v>
@@ -23873,10 +23873,10 @@
         <v>0.046677766202464</v>
       </c>
       <c r="M464" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N464" t="n">
-        <v>0.131600592202665</v>
+        <v>0.123375555189998</v>
       </c>
       <c r="O464" t="b">
         <v>0</v>
@@ -23923,10 +23923,10 @@
         <v>0.0296242465483012</v>
       </c>
       <c r="M465" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N465" t="n">
-        <v>0.12070916635232</v>
+        <v>0.0980761976612599</v>
       </c>
       <c r="O465" t="b">
         <v>0</v>
@@ -24023,10 +24023,10 @@
         <v>0.0724926808580702</v>
       </c>
       <c r="M467" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N467" t="n">
-        <v>0.136554621848739</v>
+        <v>0.126050420168067</v>
       </c>
       <c r="O467" t="b">
         <v>0</v>
@@ -24073,10 +24073,10 @@
         <v>0.0450646172100378</v>
       </c>
       <c r="M468" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N468" t="n">
-        <v>0.127595406565364</v>
+        <v>0.115995824150331</v>
       </c>
       <c r="O468" t="b">
         <v>0</v>
@@ -25073,10 +25073,10 @@
         <v>0.110430069440483</v>
       </c>
       <c r="M488" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N488" t="n">
-        <v>0.126440011239112</v>
+        <v>0.119415566170273</v>
       </c>
       <c r="O488" t="b">
         <v>0</v>
@@ -25223,10 +25223,10 @@
         <v>0.0389496885617358</v>
       </c>
       <c r="M491" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N491" t="n">
-        <v>0.128507174983937</v>
+        <v>0.121367887484829</v>
       </c>
       <c r="O491" t="b">
         <v>0</v>
@@ -25523,10 +25523,10 @@
         <v>0.0477746421121876</v>
       </c>
       <c r="M497" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N497" t="n">
-        <v>0.126187155475858</v>
+        <v>0.119545726240287</v>
       </c>
       <c r="O497" t="b">
         <v>0</v>
@@ -25708,25 +25708,25 @@
         <v>0</v>
       </c>
       <c r="H501" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I501" t="n">
         <v>11440</v>
       </c>
       <c r="J501" t="n">
-        <v>0.020801389931013</v>
+        <v>0.00611574355199338</v>
       </c>
       <c r="K501" t="n">
-        <v>0.0120190465852456</v>
+        <v>0.00198007847946259</v>
       </c>
       <c r="L501" t="n">
-        <v>0.0336595832546577</v>
+        <v>0.0143720210023291</v>
       </c>
       <c r="M501" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="N501" t="n">
-        <v>0.20979020979021</v>
+        <v>0.113636363636364</v>
       </c>
       <c r="O501" t="b">
         <v>0</v>
@@ -26008,25 +26008,25 @@
         <v>1</v>
       </c>
       <c r="H507" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I507" t="n">
         <v>25064</v>
       </c>
       <c r="J507" t="n">
-        <v>0.0400836621420999</v>
+        <v>0.0343580212331063</v>
       </c>
       <c r="K507" t="n">
-        <v>0.0219144404092806</v>
+        <v>0.0177535754106025</v>
       </c>
       <c r="L507" t="n">
-        <v>0.0672551261116439</v>
+        <v>0.0600178682649212</v>
       </c>
       <c r="M507" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N507" t="n">
-        <v>0.1915097350782</v>
+        <v>0.147622087456112</v>
       </c>
       <c r="O507" t="b">
         <v>0</v>
@@ -28858,25 +28858,25 @@
         <v>0</v>
       </c>
       <c r="H564" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I564" t="n">
         <v>11520</v>
       </c>
       <c r="J564" t="n">
-        <v>0.0295736172862716</v>
+        <v>0.021507018281864</v>
       </c>
       <c r="K564" t="n">
-        <v>0.0147585953387512</v>
+        <v>0.00928306176495268</v>
       </c>
       <c r="L564" t="n">
-        <v>0.0529494759876082</v>
+        <v>0.0424018838579632</v>
       </c>
       <c r="M564" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N564" t="n">
-        <v>0.225694444444444</v>
+        <v>0.217013888888889</v>
       </c>
       <c r="O564" t="b">
         <v>0</v>
@@ -29008,25 +29008,25 @@
         <v>0</v>
       </c>
       <c r="H567" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I567" t="n">
         <v>10905</v>
       </c>
       <c r="J567" t="n">
-        <v>0.0275575060037752</v>
+        <v>0.0206676575507732</v>
       </c>
       <c r="K567" t="n">
-        <v>0.0118955780553997</v>
+        <v>0.00758379509289306</v>
       </c>
       <c r="L567" t="n">
-        <v>0.054321188036945</v>
+        <v>0.0450013542213719</v>
       </c>
       <c r="M567" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N567" t="n">
-        <v>0.229252636405319</v>
+        <v>0.210912425492893</v>
       </c>
       <c r="O567" t="b">
         <v>0</v>
@@ -29158,25 +29158,25 @@
         <v>0</v>
       </c>
       <c r="H570" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I570" t="n">
         <v>12475</v>
       </c>
       <c r="J570" t="n">
-        <v>0.0136370964114763</v>
+        <v>0.00545462890582224</v>
       </c>
       <c r="K570" t="n">
-        <v>0.00442745015001388</v>
+        <v>0.00066055577019419</v>
       </c>
       <c r="L570" t="n">
-        <v>0.0318363832986024</v>
+        <v>0.019709866760996</v>
       </c>
       <c r="M570" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N570" t="n">
-        <v>0.224448897795591</v>
+        <v>0.208416833667335</v>
       </c>
       <c r="O570" t="b">
         <v>0</v>
@@ -29308,25 +29308,25 @@
         <v>0</v>
       </c>
       <c r="H573" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I573" t="n">
         <v>12328</v>
       </c>
       <c r="J573" t="n">
-        <v>0.0191912532398735</v>
+        <v>0.015992573804496</v>
       </c>
       <c r="K573" t="n">
-        <v>0.00704222969745841</v>
+        <v>0.0051923664353141</v>
       </c>
       <c r="L573" t="n">
-        <v>0.0417835686154211</v>
+        <v>0.0373317304023127</v>
       </c>
       <c r="M573" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N573" t="n">
-        <v>0.227125243348475</v>
+        <v>0.210902011680727</v>
       </c>
       <c r="O573" t="b">
         <v>0</v>
@@ -29458,31 +29458,31 @@
         <v>0</v>
       </c>
       <c r="H576" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I576" t="n">
         <v>13307</v>
       </c>
       <c r="J576" t="n">
-        <v>0.10111747471594</v>
+        <v>0.0519155777878052</v>
       </c>
       <c r="K576" t="n">
-        <v>0.071165616258156</v>
+        <v>0.0312481430841166</v>
       </c>
       <c r="L576" t="n">
-        <v>0.139465272582719</v>
+        <v>0.0811118354026218</v>
       </c>
       <c r="M576" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N576" t="n">
-        <v>0.225445254377395</v>
+        <v>0.210415570752236</v>
       </c>
       <c r="O576" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P576" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="577">
@@ -29608,25 +29608,25 @@
         <v>0</v>
       </c>
       <c r="H579" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I579" t="n">
         <v>12128</v>
       </c>
       <c r="J579" t="n">
-        <v>0.0339449629520754</v>
+        <v>0.0308587367775595</v>
       </c>
       <c r="K579" t="n">
-        <v>0.0169421459736257</v>
+        <v>0.014795500794455</v>
       </c>
       <c r="L579" t="n">
-        <v>0.0607616897625927</v>
+        <v>0.0567727054593955</v>
       </c>
       <c r="M579" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N579" t="n">
-        <v>0.222625329815303</v>
+        <v>0.214379947229551</v>
       </c>
       <c r="O579" t="b">
         <v>0</v>
@@ -29773,10 +29773,10 @@
         <v>0.0352892394523987</v>
       </c>
       <c r="M582" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N582" t="n">
-        <v>0.219314830220071</v>
+        <v>0.211752249867655</v>
       </c>
       <c r="O582" t="b">
         <v>0</v>
@@ -29923,10 +29923,10 @@
         <v>0.0278845987161854</v>
       </c>
       <c r="M585" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N585" t="n">
-        <v>0.227014755959137</v>
+        <v>0.21079941624777</v>
       </c>
       <c r="O585" t="b">
         <v>0</v>
@@ -30458,25 +30458,25 @@
         <v>0</v>
       </c>
       <c r="H596" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I596" t="n">
         <v>15254</v>
       </c>
       <c r="J596" t="n">
-        <v>0.0203710580025368</v>
+        <v>0.00271546282427358</v>
       </c>
       <c r="K596" t="n">
-        <v>0.0113915477656469</v>
+        <v>0.000328818909160455</v>
       </c>
       <c r="L596" t="n">
-        <v>0.0336515988196643</v>
+        <v>0.00981756422376223</v>
       </c>
       <c r="M596" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N596" t="n">
-        <v>0.13111315064901</v>
+        <v>0.052445260259604</v>
       </c>
       <c r="O596" t="b">
         <v>0</v>
@@ -30508,25 +30508,25 @@
         <v>0</v>
       </c>
       <c r="H597" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I597" t="n">
         <v>15815</v>
       </c>
       <c r="J597" t="n">
-        <v>0.032799657075656</v>
+        <v>0.0126114132115962</v>
       </c>
       <c r="K597" t="n">
-        <v>0.0213954914024525</v>
+        <v>0.00604342587140654</v>
       </c>
       <c r="L597" t="n">
-        <v>0.0481608835821294</v>
+        <v>0.0232270592944877</v>
       </c>
       <c r="M597" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N597" t="n">
-        <v>0.164400885235536</v>
+        <v>0.101169775529561</v>
       </c>
       <c r="O597" t="b">
         <v>0</v>
@@ -30658,25 +30658,25 @@
         <v>0</v>
       </c>
       <c r="H600" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I600" t="n">
         <v>16833</v>
       </c>
       <c r="J600" t="n">
-        <v>0.0219735585292906</v>
+        <v>0.0153811339451785</v>
       </c>
       <c r="K600" t="n">
-        <v>0.0105358862984922</v>
+        <v>0.00618346430474029</v>
       </c>
       <c r="L600" t="n">
-        <v>0.0404219388689806</v>
+        <v>0.0316992178963198</v>
       </c>
       <c r="M600" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="N600" t="n">
-        <v>0.201984197706885</v>
+        <v>0.106932810550704</v>
       </c>
       <c r="O600" t="b">
         <v>0</v>
@@ -31558,19 +31558,19 @@
         <v>1</v>
       </c>
       <c r="H618" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I618" t="n">
         <v>27447</v>
       </c>
       <c r="J618" t="n">
-        <v>0.0355505482855017</v>
+        <v>0.0304717803390737</v>
       </c>
       <c r="K618" t="n">
-        <v>0.0220047378752335</v>
+        <v>0.0180583402437077</v>
       </c>
       <c r="L618" t="n">
-        <v>0.0543505894412338</v>
+        <v>0.0481650636243845</v>
       </c>
       <c r="M618" t="n">
         <v>48</v>
@@ -31708,19 +31708,19 @@
         <v>1</v>
       </c>
       <c r="H621" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I621" t="n">
         <v>28361</v>
       </c>
       <c r="J621" t="n">
-        <v>0.0269374541194068</v>
+        <v>0.0232637886141089</v>
       </c>
       <c r="K621" t="n">
-        <v>0.0168789640067517</v>
+        <v>0.0140043825636776</v>
       </c>
       <c r="L621" t="n">
-        <v>0.040794452734126</v>
+        <v>0.0363383919920118</v>
       </c>
       <c r="M621" t="n">
         <v>49</v>
@@ -31858,19 +31858,19 @@
         <v>1</v>
       </c>
       <c r="H624" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I624" t="n">
         <v>28954</v>
       </c>
       <c r="J624" t="n">
-        <v>0.0442045977615435</v>
+        <v>0.0378900847306257</v>
       </c>
       <c r="K624" t="n">
-        <v>0.0273628442800269</v>
+        <v>0.0224557376051155</v>
       </c>
       <c r="L624" t="n">
-        <v>0.0675755980350443</v>
+        <v>0.0598861599154111</v>
       </c>
       <c r="M624" t="n">
         <v>50</v>
@@ -32008,25 +32008,25 @@
         <v>1</v>
       </c>
       <c r="H627" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I627" t="n">
         <v>29704</v>
       </c>
       <c r="J627" t="n">
-        <v>0.0202216016136544</v>
+        <v>0.0161773908999235</v>
       </c>
       <c r="K627" t="n">
-        <v>0.00969699270230638</v>
+        <v>0.00698423400964996</v>
       </c>
       <c r="L627" t="n">
-        <v>0.0371900619096315</v>
+        <v>0.03187735815881</v>
       </c>
       <c r="M627" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="N627" t="n">
-        <v>0.16832749798007</v>
+        <v>0.117829248586049</v>
       </c>
       <c r="O627" t="b">
         <v>0</v>
@@ -32158,25 +32158,25 @@
         <v>1</v>
       </c>
       <c r="H630" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I630" t="n">
         <v>30327</v>
       </c>
       <c r="J630" t="n">
-        <v>0.0139697534561264</v>
+        <v>0.00814882531460062</v>
       </c>
       <c r="K630" t="n">
-        <v>0.0072177446630143</v>
+        <v>0.00327607079610913</v>
       </c>
       <c r="L630" t="n">
-        <v>0.0244069981313833</v>
+        <v>0.0167923570669745</v>
       </c>
       <c r="M630" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="N630" t="n">
-        <v>0.164869588155769</v>
+        <v>0.118706103472154</v>
       </c>
       <c r="O630" t="b">
         <v>0</v>
@@ -32308,25 +32308,25 @@
         <v>1</v>
       </c>
       <c r="H633" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I633" t="n">
         <v>30815</v>
       </c>
       <c r="J633" t="n">
-        <v>0.131311493309888</v>
+        <v>0.112548222194535</v>
       </c>
       <c r="K633" t="n">
-        <v>0.106578471883313</v>
+        <v>0.0897524921377716</v>
       </c>
       <c r="L633" t="n">
-        <v>0.16007767930165</v>
+        <v>0.139383849879381</v>
       </c>
       <c r="M633" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="N633" t="n">
-        <v>0.18822002271621</v>
+        <v>0.12007139380172</v>
       </c>
       <c r="O633" t="b">
         <v>1</v>
@@ -32473,10 +32473,10 @@
         <v>0.030270213116478</v>
       </c>
       <c r="M636" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N636" t="n">
-        <v>0.22865183361182</v>
+        <v>0.211063231026295</v>
       </c>
       <c r="O636" t="b">
         <v>0</v>
@@ -32623,10 +32623,10 @@
         <v>0.0268745872187558</v>
       </c>
       <c r="M639" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N639" t="n">
-        <v>0.219522903556271</v>
+        <v>0.204888043319186</v>
       </c>
       <c r="O639" t="b">
         <v>0</v>
@@ -32773,10 +32773,10 @@
         <v>0.0332032948172558</v>
       </c>
       <c r="M642" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N642" t="n">
-        <v>0.217269414073451</v>
+        <v>0.210260723296888</v>
       </c>
       <c r="O642" t="b">
         <v>0</v>
@@ -33058,25 +33058,25 @@
         <v>0</v>
       </c>
       <c r="H648" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I648" t="n">
         <v>13149</v>
       </c>
       <c r="J648" t="n">
-        <v>0.0251557617231553</v>
+        <v>0.0232202689931648</v>
       </c>
       <c r="K648" t="n">
-        <v>0.0133877764898506</v>
+        <v>0.0119926883794306</v>
       </c>
       <c r="L648" t="n">
-        <v>0.0430583091354612</v>
+        <v>0.040598861756786</v>
       </c>
       <c r="M648" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N648" t="n">
-        <v>0.220549091185642</v>
+        <v>0.212943950110275</v>
       </c>
       <c r="O648" t="b">
         <v>0</v>
@@ -33208,25 +33208,25 @@
         <v>0</v>
       </c>
       <c r="H651" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I651" t="n">
         <v>14070</v>
       </c>
       <c r="J651" t="n">
-        <v>0.0242428210971946</v>
+        <v>0.0181812785945202</v>
       </c>
       <c r="K651" t="n">
-        <v>0.0125225576677872</v>
+        <v>0.00831150350826964</v>
       </c>
       <c r="L651" t="n">
-        <v>0.0423753772761546</v>
+        <v>0.0345343931439679</v>
       </c>
       <c r="M651" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N651" t="n">
-        <v>0.220326936744847</v>
+        <v>0.206112295664534</v>
       </c>
       <c r="O651" t="b">
         <v>0</v>
@@ -33523,10 +33523,10 @@
         <v>0.0306818887065114</v>
       </c>
       <c r="M657" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N657" t="n">
-        <v>0.220837605489392</v>
+        <v>0.212950548150485</v>
       </c>
       <c r="O657" t="b">
         <v>0</v>
@@ -33673,10 +33673,10 @@
         <v>0.0302494685346127</v>
       </c>
       <c r="M660" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N660" t="n">
-        <v>0.227346541084768</v>
+        <v>0.211107502435856</v>
       </c>
       <c r="O660" t="b">
         <v>0</v>
@@ -33823,10 +33823,10 @@
         <v>0.0251883568013486</v>
       </c>
       <c r="M663" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N663" t="n">
-        <v>0.225786359389598</v>
+        <v>0.210214886328247</v>
       </c>
       <c r="O663" t="b">
         <v>0</v>
@@ -33973,10 +33973,10 @@
         <v>0.0251865497234786</v>
       </c>
       <c r="M666" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N666" t="n">
-        <v>0.224769611148573</v>
+        <v>0.209784970405335</v>
       </c>
       <c r="O666" t="b">
         <v>0</v>
@@ -34123,10 +34123,10 @@
         <v>0.0211109336421718</v>
       </c>
       <c r="M669" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N669" t="n">
-        <v>0.224098005527751</v>
+        <v>0.209158138492567</v>
       </c>
       <c r="O669" t="b">
         <v>0</v>

--- a/results/ddPCR/SNV_data_final.xlsx
+++ b/results/ddPCR/SNV_data_final.xlsx
@@ -5270,7 +5270,7 @@
         <v>0.00458655740654583</v>
       </c>
       <c r="L92" t="n">
-        <v>0.0649899108938712</v>
+        <v>0.0649899108938713</v>
       </c>
       <c r="M92" t="n">
         <v>15</v>
@@ -6814,7 +6814,7 @@
         <v>17378</v>
       </c>
       <c r="J123" t="n">
-        <v>49.8996043885338</v>
+        <v>49.8996043885337</v>
       </c>
       <c r="K123" t="n">
         <v>49.139483664773</v>
@@ -7414,13 +7414,13 @@
         <v>14951</v>
       </c>
       <c r="J135" t="n">
-        <v>0.00593709791742938</v>
+        <v>0.00592910048452141</v>
       </c>
       <c r="K135" t="n">
-        <v>0.00161730327749761</v>
+        <v>0.00161512325920015</v>
       </c>
       <c r="L135" t="n">
-        <v>0.0152140469181478</v>
+        <v>0.0151936037739392</v>
       </c>
       <c r="M135" t="n">
         <v>17</v>
@@ -7558,19 +7558,19 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I138" t="n">
         <v>16472</v>
       </c>
       <c r="J138" t="n">
-        <v>0.0164569280588581</v>
+        <v>0.0151674090614083</v>
       </c>
       <c r="K138" t="n">
-        <v>0.00875640873553979</v>
+        <v>0.00783197210892294</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0281797678981566</v>
+        <v>0.0265292547864409</v>
       </c>
       <c r="M138" t="n">
         <v>18</v>
@@ -8008,19 +8008,19 @@
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I147" t="n">
         <v>45458</v>
       </c>
       <c r="J147" t="n">
-        <v>0.0237803171174049</v>
+        <v>0.0225861970027339</v>
       </c>
       <c r="K147" t="n">
-        <v>0.0145252895048298</v>
+        <v>0.0135980573882371</v>
       </c>
       <c r="L147" t="n">
-        <v>0.0367288965082101</v>
+        <v>0.0352731471757438</v>
       </c>
       <c r="M147" t="n">
         <v>69</v>
@@ -8214,7 +8214,7 @@
         <v>28557</v>
       </c>
       <c r="J151" t="n">
-        <v>0.0712170185979904</v>
+        <v>0.0712170185979905</v>
       </c>
       <c r="K151" t="n">
         <v>0.0460894300139205</v>
@@ -8308,19 +8308,19 @@
         <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I153" t="n">
         <v>43094</v>
       </c>
       <c r="J153" t="n">
-        <v>0.314507563935298</v>
+        <v>0.31366196417639</v>
       </c>
       <c r="K153" t="n">
-        <v>0.281988600584221</v>
+        <v>0.281184756947227</v>
       </c>
       <c r="L153" t="n">
-        <v>0.349772198537191</v>
+        <v>0.348885397284553</v>
       </c>
       <c r="M153" t="n">
         <v>66</v>
@@ -12867,7 +12867,7 @@
         <v>0.0281656435774004</v>
       </c>
       <c r="K244" t="n">
-        <v>0.0185576723626286</v>
+        <v>0.0185576723626285</v>
       </c>
       <c r="L244" t="n">
         <v>0.0409925348551718</v>
@@ -15317,10 +15317,10 @@
         <v>0.0200406285296919</v>
       </c>
       <c r="K293" t="n">
-        <v>0.00242723715163795</v>
+        <v>0.00242723715163796</v>
       </c>
       <c r="L293" t="n">
-        <v>0.0723854955259818</v>
+        <v>0.0723854955259819</v>
       </c>
       <c r="M293" t="n">
         <v>15</v>
@@ -16270,7 +16270,7 @@
         <v>0.00750427414216105</v>
       </c>
       <c r="L312" t="n">
-        <v>0.0705123253394388</v>
+        <v>0.0705123253394389</v>
       </c>
       <c r="M312" t="n">
         <v>13</v>
@@ -19317,7 +19317,7 @@
         <v>0.0200722200493538</v>
       </c>
       <c r="K373" t="n">
-        <v>0.0073657977981381</v>
+        <v>0.00736579779813811</v>
       </c>
       <c r="L373" t="n">
         <v>0.0436971452173887</v>
@@ -19417,7 +19417,7 @@
         <v>0.0215618065106053</v>
       </c>
       <c r="K375" t="n">
-        <v>0.00791229957544402</v>
+        <v>0.00791229957544404</v>
       </c>
       <c r="L375" t="n">
         <v>0.0469420772746819</v>
@@ -20314,13 +20314,13 @@
         <v>13593</v>
       </c>
       <c r="J393" t="n">
-        <v>0.016431396935137</v>
+        <v>0.0163826295301539</v>
       </c>
       <c r="K393" t="n">
-        <v>0.00847987815483543</v>
+        <v>0.00845458728775358</v>
       </c>
       <c r="L393" t="n">
-        <v>0.0287691407221729</v>
+        <v>0.0286844752161368</v>
       </c>
       <c r="M393" t="n">
         <v>15</v>
@@ -23317,7 +23317,7 @@
         <v>0.00790401994678377</v>
       </c>
       <c r="K453" t="n">
-        <v>0.000957207820179326</v>
+        <v>0.000957207820179324</v>
       </c>
       <c r="L453" t="n">
         <v>0.0285559013965602</v>
@@ -25708,19 +25708,19 @@
         <v>0</v>
       </c>
       <c r="H501" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I501" t="n">
         <v>11440</v>
       </c>
       <c r="J501" t="n">
-        <v>0.00611574355199338</v>
+        <v>0.00489244079125493</v>
       </c>
       <c r="K501" t="n">
-        <v>0.00198007847946259</v>
+        <v>0.00133003913336018</v>
       </c>
       <c r="L501" t="n">
-        <v>0.0143720210023291</v>
+        <v>0.0126088195435542</v>
       </c>
       <c r="M501" t="n">
         <v>13</v>
@@ -30664,13 +30664,13 @@
         <v>16833</v>
       </c>
       <c r="J600" t="n">
-        <v>0.0153811339451785</v>
+        <v>0.0153609369317713</v>
       </c>
       <c r="K600" t="n">
-        <v>0.00618346430474029</v>
+        <v>0.00617534288574729</v>
       </c>
       <c r="L600" t="n">
-        <v>0.0316992178963198</v>
+        <v>0.0316576161899308</v>
       </c>
       <c r="M600" t="n">
         <v>18</v>
@@ -32314,13 +32314,13 @@
         <v>30815</v>
       </c>
       <c r="J633" t="n">
-        <v>0.112548222194535</v>
+        <v>0.112514260776809</v>
       </c>
       <c r="K633" t="n">
-        <v>0.0897524921377716</v>
+        <v>0.0897253950989989</v>
       </c>
       <c r="L633" t="n">
-        <v>0.139383849879381</v>
+        <v>0.139341817843436</v>
       </c>
       <c r="M633" t="n">
         <v>37</v>
@@ -33017,7 +33017,7 @@
         <v>0.00428434157460931</v>
       </c>
       <c r="K647" t="n">
-        <v>0.000518817658943747</v>
+        <v>0.000518817658943746</v>
       </c>
       <c r="L647" t="n">
         <v>0.0154845381479274</v>

--- a/results/ddPCR/SNV_data_final.xlsx
+++ b/results/ddPCR/SNV_data_final.xlsx
@@ -9508,19 +9508,19 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I177" t="n">
         <v>15056</v>
       </c>
       <c r="J177" t="n">
-        <v>0.0180140131218616</v>
+        <v>0.0140105291155955</v>
       </c>
       <c r="K177" t="n">
-        <v>0.00823544772020317</v>
+        <v>0.00563202260818086</v>
       </c>
       <c r="L177" t="n">
-        <v>0.0342129340852272</v>
+        <v>0.0288800348467268</v>
       </c>
       <c r="M177" t="n">
         <v>15</v>
@@ -9808,19 +9808,19 @@
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I183" t="n">
         <v>15160</v>
       </c>
       <c r="J183" t="n">
-        <v>0.00386801771462629</v>
+        <v>0.00309433603066978</v>
       </c>
       <c r="K183" t="n">
-        <v>0.00124576515395246</v>
+        <v>0.000837757741890053</v>
       </c>
       <c r="L183" t="n">
-        <v>0.00915300220202122</v>
+        <v>0.00802668781386873</v>
       </c>
       <c r="M183" t="n">
         <v>15</v>
@@ -9958,19 +9958,19 @@
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I186" t="n">
         <v>16723</v>
       </c>
       <c r="J186" t="n">
-        <v>0.0109416864386727</v>
+        <v>0.00683822107958527</v>
       </c>
       <c r="K186" t="n">
-        <v>0.00472218689205414</v>
+        <v>0.00221984952625984</v>
       </c>
       <c r="L186" t="n">
-        <v>0.0215777586995252</v>
+        <v>0.0159697890654529</v>
       </c>
       <c r="M186" t="n">
         <v>17</v>
@@ -10408,19 +10408,19 @@
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I195" t="n">
         <v>15775</v>
       </c>
       <c r="J195" t="n">
-        <v>0.00644195909236445</v>
+        <v>0.00536818668996907</v>
       </c>
       <c r="K195" t="n">
-        <v>0.00236206040287471</v>
+        <v>0.0017417916340444</v>
       </c>
       <c r="L195" t="n">
-        <v>0.0140533441454258</v>
+        <v>0.0125545264885204</v>
       </c>
       <c r="M195" t="n">
         <v>16</v>
@@ -10708,19 +10708,19 @@
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I201" t="n">
         <v>16123</v>
       </c>
       <c r="J201" t="n">
-        <v>0.0138703454972834</v>
+        <v>0.0107877097144092</v>
       </c>
       <c r="K201" t="n">
-        <v>0.00634039185722858</v>
+        <v>0.00433611178850993</v>
       </c>
       <c r="L201" t="n">
-        <v>0.0263494343287488</v>
+        <v>0.0222417110583841</v>
       </c>
       <c r="M201" t="n">
         <v>16</v>
@@ -11008,19 +11008,19 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I207" t="n">
         <v>17518</v>
       </c>
       <c r="J207" t="n">
-        <v>0.00286188336610586</v>
+        <v>0.00214636661013578</v>
       </c>
       <c r="K207" t="n">
-        <v>0.000777471556591257</v>
+        <v>0.000441723923556918</v>
       </c>
       <c r="L207" t="n">
-        <v>0.00738484101818401</v>
+        <v>0.00631801355512601</v>
       </c>
       <c r="M207" t="n">
         <v>17</v>
@@ -11458,19 +11458,19 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I216" t="n">
         <v>16294</v>
       </c>
       <c r="J216" t="n">
-        <v>0.01164696004485</v>
+        <v>0.010093568928626</v>
       </c>
       <c r="K216" t="n">
-        <v>0.00645400111052113</v>
+        <v>0.00532643208135552</v>
       </c>
       <c r="L216" t="n">
-        <v>0.0194464336946081</v>
+        <v>0.0174619011630262</v>
       </c>
       <c r="M216" t="n">
         <v>16</v>
@@ -11758,19 +11758,19 @@
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I222" t="n">
         <v>17828</v>
       </c>
       <c r="J222" t="n">
-        <v>0.00632864822240416</v>
+        <v>0.00361616416710011</v>
       </c>
       <c r="K222" t="n">
-        <v>0.00254166379703963</v>
+        <v>0.000984675377769694</v>
       </c>
       <c r="L222" t="n">
-        <v>0.0130733784213051</v>
+        <v>0.00927917197455792</v>
       </c>
       <c r="M222" t="n">
         <v>18</v>
@@ -11908,19 +11908,19 @@
         <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I225" t="n">
         <v>17488</v>
       </c>
       <c r="J225" t="n">
-        <v>0.00238130473304697</v>
+        <v>0.00158750369645045</v>
       </c>
       <c r="K225" t="n">
-        <v>0.000490590594308017</v>
+        <v>0.000192150039561377</v>
       </c>
       <c r="L225" t="n">
-        <v>0.00698832151815359</v>
+        <v>0.00575644720397774</v>
       </c>
       <c r="M225" t="n">
         <v>17</v>
@@ -12308,19 +12308,19 @@
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I233" t="n">
         <v>15330</v>
       </c>
       <c r="J233" t="n">
-        <v>0.0244668432777965</v>
+        <v>0.0203579310343545</v>
       </c>
       <c r="K233" t="n">
-        <v>0.0126394000912042</v>
+        <v>0.00976042910112069</v>
       </c>
       <c r="L233" t="n">
-        <v>0.0427595849337368</v>
+        <v>0.0374562081793538</v>
       </c>
       <c r="M233" t="n">
         <v>15</v>
@@ -12414,13 +12414,13 @@
         <v>16937</v>
       </c>
       <c r="J235" t="n">
-        <v>0.00558923452787199</v>
+        <v>0.00557931678344893</v>
       </c>
       <c r="K235" t="n">
-        <v>0.00115257146152937</v>
+        <v>0.00115052601099749</v>
       </c>
       <c r="L235" t="n">
-        <v>0.0163387422632032</v>
+        <v>0.016309768184658</v>
       </c>
       <c r="M235" t="n">
         <v>17</v>
@@ -13664,13 +13664,13 @@
         <v>14770</v>
       </c>
       <c r="J260" t="n">
-        <v>0.010104659492478</v>
+        <v>0.0101330276124825</v>
       </c>
       <c r="K260" t="n">
-        <v>0.00370733550802742</v>
+        <v>0.00371775050353731</v>
       </c>
       <c r="L260" t="n">
-        <v>0.0220088761699113</v>
+        <v>0.0220705523385981</v>
       </c>
       <c r="M260" t="n">
         <v>21</v>
@@ -13964,13 +13964,13 @@
         <v>15018</v>
       </c>
       <c r="J266" t="n">
-        <v>0.00971476049210114</v>
+        <v>0.00971841999791206</v>
       </c>
       <c r="K266" t="n">
-        <v>0.00264679067514426</v>
+        <v>0.00264778787220649</v>
       </c>
       <c r="L266" t="n">
-        <v>0.0248799367989624</v>
+        <v>0.0248893039967551</v>
       </c>
       <c r="M266" t="n">
         <v>21</v>
@@ -14514,13 +14514,13 @@
         <v>15549</v>
       </c>
       <c r="J277" t="n">
-        <v>0.0264174201426192</v>
+        <v>0.0264228987202176</v>
       </c>
       <c r="K277" t="n">
-        <v>0.010621110056127</v>
+        <v>0.0106233130904565</v>
       </c>
       <c r="L277" t="n">
-        <v>0.0544348902415863</v>
+        <v>0.0544461756952827</v>
       </c>
       <c r="M277" t="n">
         <v>25</v>
@@ -15164,13 +15164,13 @@
         <v>23524</v>
       </c>
       <c r="J290" t="n">
-        <v>0.0121185532369918</v>
+        <v>0.0121202499026388</v>
       </c>
       <c r="K290" t="n">
-        <v>0.00393485490791686</v>
+        <v>0.00393540585928918</v>
       </c>
       <c r="L290" t="n">
-        <v>0.0282823475707711</v>
+        <v>0.0282863065095344</v>
       </c>
       <c r="M290" t="n">
         <v>31</v>
@@ -16370,7 +16370,7 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0.00398276305335548</v>
+        <v>0.00401294849471934</v>
       </c>
       <c r="M314" t="n">
         <v>22</v>
@@ -17158,19 +17158,19 @@
         <v>0</v>
       </c>
       <c r="H330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I330" t="n">
         <v>16209</v>
       </c>
       <c r="J330" t="n">
-        <v>0.00148541725906939</v>
+        <v>0.000742691233945346</v>
       </c>
       <c r="K330" t="n">
-        <v>0.000179585180102617</v>
+        <v>0.0000187968917739303</v>
       </c>
       <c r="L330" t="n">
-        <v>0.00541368330659393</v>
+        <v>0.00417050781509146</v>
       </c>
       <c r="M330" t="n">
         <v>16</v>
@@ -17308,19 +17308,19 @@
         <v>0</v>
       </c>
       <c r="H333" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I333" t="n">
         <v>15925</v>
       </c>
       <c r="J333" t="n">
-        <v>0.00259623425532269</v>
+        <v>0.00129805245430271</v>
       </c>
       <c r="K333" t="n">
-        <v>0.000689307526978192</v>
+        <v>0.000155664981042168</v>
       </c>
       <c r="L333" t="n">
-        <v>0.00682436201747195</v>
+        <v>0.00479400385863599</v>
       </c>
       <c r="M333" t="n">
         <v>16</v>
@@ -17758,19 +17758,19 @@
         <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I342" t="n">
         <v>16877</v>
       </c>
       <c r="J342" t="n">
-        <v>0.00232247473681316</v>
+        <v>0.000774124358075731</v>
       </c>
       <c r="K342" t="n">
-        <v>0.000478198256287262</v>
+        <v>0.0000195956356421816</v>
       </c>
       <c r="L342" t="n">
-        <v>0.00682772868471219</v>
+        <v>0.00433375089711716</v>
       </c>
       <c r="M342" t="n">
         <v>17</v>
@@ -17914,13 +17914,13 @@
         <v>15897</v>
       </c>
       <c r="J345" t="n">
-        <v>0.00118307490208265</v>
+        <v>0.00118021087124745</v>
       </c>
       <c r="K345" t="n">
-        <v>0.0000299515088899638</v>
+        <v>0.0000298789936075782</v>
       </c>
       <c r="L345" t="n">
-        <v>0.00659826140969555</v>
+        <v>0.0065823451561835</v>
       </c>
       <c r="M345" t="n">
         <v>16</v>
@@ -22514,13 +22514,13 @@
         <v>24554</v>
       </c>
       <c r="J437" t="n">
-        <v>0.00583610303874001</v>
+        <v>0.00583749109460355</v>
       </c>
       <c r="K437" t="n">
-        <v>0.00159008269262548</v>
+        <v>0.00159046091568348</v>
       </c>
       <c r="L437" t="n">
-        <v>0.0149451436064332</v>
+        <v>0.0149486969544557</v>
       </c>
       <c r="M437" t="n">
         <v>32</v>

--- a/results/ddPCR/SNV_data_final.xlsx
+++ b/results/ddPCR/SNV_data_final.xlsx
@@ -4370,10 +4370,10 @@
         <v>0.0395112628427656</v>
       </c>
       <c r="M74" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="N74" t="n">
-        <v>0.122309197651663</v>
+        <v>0.220156555772994</v>
       </c>
       <c r="O74" t="b">
         <v>0</v>
@@ -4520,10 +4520,10 @@
         <v>0.0318750230176824</v>
       </c>
       <c r="M77" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="N77" t="n">
-        <v>0.118260869565217</v>
+        <v>0.215652173913043</v>
       </c>
       <c r="O77" t="b">
         <v>0</v>
@@ -4670,10 +4670,10 @@
         <v>0.0214716780735992</v>
       </c>
       <c r="M80" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="N80" t="n">
-        <v>0.122766334742873</v>
+        <v>0.211430909834947</v>
       </c>
       <c r="O80" t="b">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0.0396867753506377</v>
       </c>
       <c r="M83" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="N83" t="n">
-        <v>0.122438984572688</v>
+        <v>0.220390172230838</v>
       </c>
       <c r="O83" t="b">
         <v>0</v>
@@ -4970,10 +4970,10 @@
         <v>0.0474790543977189</v>
       </c>
       <c r="M86" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="N86" t="n">
-        <v>0.117411423440845</v>
+        <v>0.214103183921542</v>
       </c>
       <c r="O86" t="b">
         <v>0</v>
@@ -5120,10 +5120,10 @@
         <v>0.117633304299542</v>
       </c>
       <c r="M89" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="N89" t="n">
-        <v>0.119579081632653</v>
+        <v>0.215242346938776</v>
       </c>
       <c r="O89" t="b">
         <v>0</v>
@@ -5270,10 +5270,10 @@
         <v>0.0198464966523898</v>
       </c>
       <c r="M92" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N92" t="n">
-        <v>0.122425464496615</v>
+        <v>0.216044937346968</v>
       </c>
       <c r="O92" t="b">
         <v>0</v>
@@ -5420,10 +5420,10 @@
         <v>0.0649899108938713</v>
       </c>
       <c r="M95" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="N95" t="n">
-        <v>0.121911573472042</v>
+        <v>0.219440832249675</v>
       </c>
       <c r="O95" t="b">
         <v>0</v>
@@ -5570,10 +5570,10 @@
         <v>0.057776992013009</v>
       </c>
       <c r="M98" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N98" t="n">
-        <v>0.121680624150025</v>
+        <v>0.214730513205927</v>
       </c>
       <c r="O98" t="b">
         <v>0</v>
@@ -5720,10 +5720,10 @@
         <v>0.0183983169247508</v>
       </c>
       <c r="M101" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="N101" t="n">
-        <v>0.126508369015181</v>
+        <v>0.223822499026859</v>
       </c>
       <c r="O101" t="b">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0.0120817225587311</v>
       </c>
       <c r="M104" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="N104" t="n">
-        <v>0.125225013696486</v>
+        <v>0.21914377396885</v>
       </c>
       <c r="O104" t="b">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0.0205912448556729</v>
       </c>
       <c r="M236" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N236" t="n">
-        <v>0.122699386503067</v>
+        <v>0.0649584987369181</v>
       </c>
       <c r="O236" t="b">
         <v>0</v>
@@ -12520,10 +12520,10 @@
         <v>0.0285345552384346</v>
       </c>
       <c r="M237" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N237" t="n">
-        <v>0.0989201220014838</v>
+        <v>0.0659467480009892</v>
       </c>
       <c r="O237" t="b">
         <v>0</v>
@@ -12620,10 +12620,10 @@
         <v>0.0274987554911442</v>
       </c>
       <c r="M239" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N239" t="n">
-        <v>0.117975783918038</v>
+        <v>0.0620925178515989</v>
       </c>
       <c r="O239" t="b">
         <v>0</v>
@@ -12670,13 +12670,13 @@
         <v>0.0585564719758217</v>
       </c>
       <c r="M240" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N240" t="n">
-        <v>0.103775844176579</v>
+        <v>0.0718448151991698</v>
       </c>
       <c r="O240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P240" t="b">
         <v>0</v>
@@ -12770,10 +12770,10 @@
         <v>0.0161459719868957</v>
       </c>
       <c r="M242" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N242" t="n">
-        <v>0.122009082898394</v>
+        <v>0.0677828238324409</v>
       </c>
       <c r="O242" t="b">
         <v>0</v>
@@ -12820,10 +12820,10 @@
         <v>0.0181490643352089</v>
       </c>
       <c r="M243" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N243" t="n">
-        <v>0.100050025012506</v>
+        <v>0.0643178732223254</v>
       </c>
       <c r="O243" t="b">
         <v>0</v>
@@ -12920,10 +12920,10 @@
         <v>0.0175636231781437</v>
       </c>
       <c r="M245" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N245" t="n">
-        <v>0.117970900511207</v>
+        <v>0.0655393891728929</v>
       </c>
       <c r="O245" t="b">
         <v>0</v>
@@ -12970,10 +12970,10 @@
         <v>0.0157044971918804</v>
       </c>
       <c r="M246" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N246" t="n">
-        <v>0.103542637378892</v>
+        <v>0.0665631240292878</v>
       </c>
       <c r="O246" t="b">
         <v>0</v>
@@ -13220,10 +13220,10 @@
         <v>0.112223546186696</v>
       </c>
       <c r="M251" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N251" t="n">
-        <v>0.125740973594396</v>
+        <v>0.0718519849110832</v>
       </c>
       <c r="O251" t="b">
         <v>0</v>
@@ -13270,10 +13270,10 @@
         <v>0.0258888550888256</v>
       </c>
       <c r="M252" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N252" t="n">
-        <v>0.109051254089422</v>
+        <v>0.0693962526023595</v>
       </c>
       <c r="O252" t="b">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0.023170510100858</v>
       </c>
       <c r="M269" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N269" t="n">
-        <v>0.119323366322735</v>
+        <v>0.0631711939355654</v>
       </c>
       <c r="O269" t="b">
         <v>0</v>
@@ -14170,10 +14170,10 @@
         <v>0.039475269172782</v>
       </c>
       <c r="M270" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N270" t="n">
-        <v>0.102467092299204</v>
+        <v>0.0709387562071412</v>
       </c>
       <c r="O270" t="b">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0.0180421879892845</v>
       </c>
       <c r="M272" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N272" t="n">
-        <v>0.120404559319313</v>
+        <v>0.0642157649703002</v>
       </c>
       <c r="O272" t="b">
         <v>0</v>
@@ -14320,10 +14320,10 @@
         <v>0.0157835464883712</v>
       </c>
       <c r="M273" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N273" t="n">
-        <v>0.0987466767945309</v>
+        <v>0.0683630839346753</v>
       </c>
       <c r="O273" t="b">
         <v>0</v>
@@ -14420,10 +14420,10 @@
         <v>0.0442013196579361</v>
       </c>
       <c r="M275" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N275" t="n">
-        <v>0.128128470146066</v>
+        <v>0.0683351840779021</v>
       </c>
       <c r="O275" t="b">
         <v>0</v>
@@ -14470,10 +14470,10 @@
         <v>0.02516111023792</v>
       </c>
       <c r="M276" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N276" t="n">
-        <v>0.104602510460251</v>
+        <v>0.0643707756678468</v>
       </c>
       <c r="O276" t="b">
         <v>0</v>
@@ -14870,10 +14870,10 @@
         <v>0.0312896121744421</v>
       </c>
       <c r="M284" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N284" t="n">
-        <v>0.123690937577307</v>
+        <v>0.0659685000412303</v>
       </c>
       <c r="O284" t="b">
         <v>0</v>
@@ -15020,10 +15020,10 @@
         <v>0.0352662913381714</v>
       </c>
       <c r="M287" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N287" t="n">
-        <v>0.118422026496928</v>
+        <v>0.0666123899045222</v>
       </c>
       <c r="O287" t="b">
         <v>0</v>
@@ -15070,10 +15070,10 @@
         <v>0.0420348170760134</v>
       </c>
       <c r="M288" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N288" t="n">
-        <v>0.105613778536031</v>
+        <v>0.0649930944837111</v>
       </c>
       <c r="O288" t="b">
         <v>0</v>
@@ -15220,10 +15220,10 @@
         <v>0.0366602215738631</v>
       </c>
       <c r="M291" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N291" t="n">
-        <v>0.106356868199296</v>
+        <v>0.0654503804303363</v>
       </c>
       <c r="O291" t="b">
         <v>0</v>
@@ -15320,10 +15320,10 @@
         <v>0.0282236923226029</v>
       </c>
       <c r="M293" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N293" t="n">
-        <v>0.119980803071509</v>
+        <v>0.0639897616381379</v>
       </c>
       <c r="O293" t="b">
         <v>0</v>
@@ -15370,10 +15370,10 @@
         <v>0.0114347000556112</v>
       </c>
       <c r="M294" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N294" t="n">
-        <v>0.101996211569285</v>
+        <v>0.0655689931516829</v>
       </c>
       <c r="O294" t="b">
         <v>0</v>
@@ -15470,10 +15470,10 @@
         <v>0.0723854955259819</v>
       </c>
       <c r="M296" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N296" t="n">
-        <v>0.124409056979348</v>
+        <v>0.0663514970556523</v>
       </c>
       <c r="O296" t="b">
         <v>0</v>
@@ -15620,10 +15620,10 @@
         <v>0.0556467609877703</v>
       </c>
       <c r="M299" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N299" t="n">
-        <v>0.119751515605119</v>
+        <v>0.0673602275278797</v>
       </c>
       <c r="O299" t="b">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0.0231906518093525</v>
       </c>
       <c r="M300" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N300" t="n">
-        <v>0.103450823911919</v>
+        <v>0.0665041010862337</v>
       </c>
       <c r="O300" t="b">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0.0515802787637369</v>
       </c>
       <c r="M302" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N302" t="n">
-        <v>0.121645252033757</v>
+        <v>0.0684254542689881</v>
       </c>
       <c r="O302" t="b">
         <v>0</v>
@@ -15820,10 +15820,10 @@
         <v>0.0416781170232105</v>
       </c>
       <c r="M303" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N303" t="n">
-        <v>0.103757503890906</v>
+        <v>0.066701252501297</v>
       </c>
       <c r="O303" t="b">
         <v>0</v>
@@ -15970,10 +15970,10 @@
         <v>0.0370378102646554</v>
       </c>
       <c r="M306" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N306" t="n">
-        <v>0.103610424802742</v>
+        <v>0.0717302940942058</v>
       </c>
       <c r="O306" t="b">
         <v>0</v>
@@ -16420,10 +16420,10 @@
         <v>0.0705123253394389</v>
       </c>
       <c r="M315" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N315" t="n">
-        <v>0.103626943005181</v>
+        <v>0.0956556396970905</v>
       </c>
       <c r="O315" t="b">
         <v>0</v>
@@ -18770,10 +18770,10 @@
         <v>0.0430586168578055</v>
       </c>
       <c r="M362" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N362" t="n">
-        <v>0.126606934164394</v>
+        <v>0.175301908843007</v>
       </c>
       <c r="O362" t="b">
         <v>0</v>
@@ -18820,10 +18820,10 @@
         <v>0.0389218766135965</v>
       </c>
       <c r="M363" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N363" t="n">
-        <v>0.105160977188157</v>
+        <v>0.161786118751011</v>
       </c>
       <c r="O363" t="b">
         <v>0</v>
@@ -18920,10 +18920,10 @@
         <v>0.054462695541228</v>
       </c>
       <c r="M365" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N365" t="n">
-        <v>0.120792398131744</v>
+        <v>0.169109357384442</v>
       </c>
       <c r="O365" t="b">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0.0469420772746819</v>
       </c>
       <c r="M366" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N366" t="n">
-        <v>0.106522451655195</v>
+        <v>0.155686660111439</v>
       </c>
       <c r="O366" t="b">
         <v>0</v>
@@ -19070,10 +19070,10 @@
         <v>0.0565582706433835</v>
       </c>
       <c r="M368" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N368" t="n">
-        <v>0.126054494327548</v>
+        <v>0.174536992145835</v>
       </c>
       <c r="O368" t="b">
         <v>0</v>
@@ -19120,10 +19120,10 @@
         <v>0.0476175038836019</v>
       </c>
       <c r="M369" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N369" t="n">
-        <v>0.0989690721649484</v>
+        <v>0.156701030927835</v>
       </c>
       <c r="O369" t="b">
         <v>0</v>
@@ -19220,10 +19220,10 @@
         <v>0.0563735440157395</v>
       </c>
       <c r="M371" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N371" t="n">
-        <v>0.120163422254266</v>
+        <v>0.176239685972923</v>
       </c>
       <c r="O371" t="b">
         <v>0</v>
@@ -19270,10 +19270,10 @@
         <v>0.0403137701892689</v>
       </c>
       <c r="M372" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="N372" t="n">
-        <v>0.100893629287979</v>
+        <v>0.158547131738253</v>
       </c>
       <c r="O372" t="b">
         <v>0</v>
@@ -19370,10 +19370,10 @@
         <v>0.0574015638089767</v>
       </c>
       <c r="M374" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N374" t="n">
-        <v>0.12421331566744</v>
+        <v>0.173898641934415</v>
       </c>
       <c r="O374" t="b">
         <v>0</v>
@@ -19420,10 +19420,10 @@
         <v>0.0434376834193166</v>
       </c>
       <c r="M375" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N375" t="n">
-        <v>0.104175709697022</v>
+        <v>0.164944873686952</v>
       </c>
       <c r="O375" t="b">
         <v>0</v>
@@ -19520,10 +19520,10 @@
         <v>0.0712938227114923</v>
       </c>
       <c r="M377" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N377" t="n">
-        <v>0.125659713495853</v>
+        <v>0.175923598894195</v>
       </c>
       <c r="O377" t="b">
         <v>0</v>
@@ -19570,10 +19570,10 @@
         <v>0.0465209592419369</v>
       </c>
       <c r="M378" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N378" t="n">
-        <v>0.108774474256708</v>
+        <v>0.169204737732657</v>
       </c>
       <c r="O378" t="b">
         <v>0</v>
@@ -19670,10 +19670,10 @@
         <v>0.0932002144417741</v>
       </c>
       <c r="M380" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N380" t="n">
-        <v>0.120753501851554</v>
+        <v>0.064401867654162</v>
       </c>
       <c r="O380" t="b">
         <v>0</v>
@@ -19720,13 +19720,13 @@
         <v>0.0450347114330441</v>
       </c>
       <c r="M381" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N381" t="n">
-        <v>0.101825017623561</v>
+        <v>0.0704942429701574</v>
       </c>
       <c r="O381" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P381" t="b">
         <v>0</v>
@@ -19970,10 +19970,10 @@
         <v>0.0633946848437411</v>
       </c>
       <c r="M386" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N386" t="n">
-        <v>0.12100128563866</v>
+        <v>0.0680632231717462</v>
       </c>
       <c r="O386" t="b">
         <v>0</v>
@@ -20020,10 +20020,10 @@
         <v>0.0823908096815058</v>
       </c>
       <c r="M387" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N387" t="n">
-        <v>0.104300385109114</v>
+        <v>0.0722079589216945</v>
       </c>
       <c r="O387" t="b">
         <v>0</v>
@@ -20120,10 +20120,10 @@
         <v>0.0537437457968037</v>
       </c>
       <c r="M389" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N389" t="n">
-        <v>0.12347711557458</v>
+        <v>0.0658544616397761</v>
       </c>
       <c r="O389" t="b">
         <v>0</v>
@@ -20170,10 +20170,10 @@
         <v>0.0201077019473549</v>
       </c>
       <c r="M390" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N390" t="n">
-        <v>0.106765019897117</v>
+        <v>0.0679413762981656</v>
       </c>
       <c r="O390" t="b">
         <v>0</v>
@@ -20270,10 +20270,10 @@
         <v>0.0441196797022246</v>
       </c>
       <c r="M392" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N392" t="n">
-        <v>0.126230749810654</v>
+        <v>0.0673230665656821</v>
       </c>
       <c r="O392" t="b">
         <v>0</v>
@@ -20320,10 +20320,10 @@
         <v>0.0163621468962998</v>
       </c>
       <c r="M393" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N393" t="n">
-        <v>0.0988467874794069</v>
+        <v>0.0658978583196046</v>
       </c>
       <c r="O393" t="b">
         <v>0</v>
@@ -20570,10 +20570,10 @@
         <v>0.0870756405949396</v>
       </c>
       <c r="M398" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N398" t="n">
-        <v>0.121477162293489</v>
+        <v>0.170068027210884</v>
       </c>
       <c r="O398" t="b">
         <v>0</v>
@@ -20620,10 +20620,10 @@
         <v>0.0871697045874413</v>
       </c>
       <c r="M399" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N399" t="n">
-        <v>0.108479479298499</v>
+        <v>0.162719218947749</v>
       </c>
       <c r="O399" t="b">
         <v>0</v>
@@ -20720,10 +20720,10 @@
         <v>0.0589846098359881</v>
       </c>
       <c r="M401" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N401" t="n">
-        <v>0.128789379829602</v>
+        <v>0.178323756687141</v>
       </c>
       <c r="O401" t="b">
         <v>0</v>
@@ -20770,10 +20770,10 @@
         <v>0.0279766495171053</v>
       </c>
       <c r="M402" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="N402" t="n">
-        <v>0.0986941998177953</v>
+        <v>0.159429092013362</v>
       </c>
       <c r="O402" t="b">
         <v>0</v>
@@ -20870,10 +20870,10 @@
         <v>0.0501047152868525</v>
       </c>
       <c r="M404" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N404" t="n">
-        <v>0.120375571783966</v>
+        <v>0.176550838616483</v>
       </c>
       <c r="O404" t="b">
         <v>0</v>
@@ -20920,10 +20920,10 @@
         <v>0.0346669668364871</v>
       </c>
       <c r="M405" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="N405" t="n">
-        <v>0.100177236649457</v>
+        <v>0.161824766895276</v>
       </c>
       <c r="O405" t="b">
         <v>0</v>
@@ -21020,10 +21020,10 @@
         <v>0.047367602281753</v>
       </c>
       <c r="M407" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="N407" t="n">
-        <v>0.119967009072505</v>
+        <v>0.172452575541726</v>
       </c>
       <c r="O407" t="b">
         <v>0</v>
@@ -21070,10 +21070,10 @@
         <v>0.0940611559363081</v>
       </c>
       <c r="M408" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N408" t="n">
-        <v>0.103355064398156</v>
+        <v>0.159007791381778</v>
       </c>
       <c r="O408" t="b">
         <v>0</v>
@@ -21170,10 +21170,10 @@
         <v>0.0566139855181378</v>
       </c>
       <c r="M410" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N410" t="n">
-        <v>0.125763564498742</v>
+        <v>0.179662234998203</v>
       </c>
       <c r="O410" t="b">
         <v>0</v>
@@ -21220,10 +21220,10 @@
         <v>0.0908277658639352</v>
       </c>
       <c r="M411" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N411" t="n">
-        <v>0.112828613336342</v>
+        <v>0.169242920004513</v>
       </c>
       <c r="O411" t="b">
         <v>0</v>
@@ -21470,10 +21470,10 @@
         <v>0.0474261277526193</v>
       </c>
       <c r="M416" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N416" t="n">
-        <v>0.120804210889637</v>
+        <v>0.172577444128052</v>
       </c>
       <c r="O416" t="b">
         <v>0</v>
@@ -21520,10 +21520,10 @@
         <v>0.0718408536621055</v>
       </c>
       <c r="M417" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="N417" t="n">
-        <v>0.0988979937835547</v>
+        <v>0.155411133088443</v>
       </c>
       <c r="O417" t="b">
         <v>0</v>
@@ -21620,10 +21620,10 @@
         <v>0.127185674566487</v>
       </c>
       <c r="M419" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N419" t="n">
-        <v>0.125920185974429</v>
+        <v>0.174351026733824</v>
       </c>
       <c r="O419" t="b">
         <v>0</v>
@@ -21670,10 +21670,10 @@
         <v>0.0594746595237704</v>
       </c>
       <c r="M420" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N420" t="n">
-        <v>0.105064089094348</v>
+        <v>0.168102542550956</v>
       </c>
       <c r="O420" t="b">
         <v>0</v>
@@ -21770,10 +21770,10 @@
         <v>0.032636639322883</v>
       </c>
       <c r="M422" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N422" t="n">
-        <v>0.122337363270006</v>
+        <v>0.172711571675302</v>
       </c>
       <c r="O422" t="b">
         <v>0</v>
@@ -21820,13 +21820,13 @@
         <v>0.133973038988039</v>
       </c>
       <c r="M423" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N423" t="n">
-        <v>0.105374077976818</v>
+        <v>0.158061116965227</v>
       </c>
       <c r="O423" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P423" t="b">
         <v>0</v>
@@ -21970,10 +21970,10 @@
         <v>0.0318281718061333</v>
       </c>
       <c r="M426" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N426" t="n">
-        <v>0.103404390709513</v>
+        <v>0.159083678014636</v>
       </c>
       <c r="O426" t="b">
         <v>0</v>
@@ -22070,10 +22070,10 @@
         <v>0.0548705102126687</v>
       </c>
       <c r="M428" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N428" t="n">
-        <v>0.131737841695027</v>
+        <v>0.186628609067955</v>
       </c>
       <c r="O428" t="b">
         <v>0</v>
@@ -22370,10 +22370,10 @@
         <v>0.0216268712241299</v>
       </c>
       <c r="M434" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N434" t="n">
-        <v>0.121546065958998</v>
+        <v>0.0648245685114658</v>
       </c>
       <c r="O434" t="b">
         <v>0</v>
@@ -22520,10 +22520,10 @@
         <v>0.0677277285332524</v>
       </c>
       <c r="M437" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N437" t="n">
-        <v>0.121310149615851</v>
+        <v>0.0646987464617873</v>
       </c>
       <c r="O437" t="b">
         <v>0</v>
@@ -22570,10 +22570,10 @@
         <v>0.0105891572505972</v>
       </c>
       <c r="M438" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N438" t="n">
-        <v>0.102774922918808</v>
+        <v>0.0711518697130208</v>
       </c>
       <c r="O438" t="b">
         <v>0</v>
@@ -22720,10 +22720,10 @@
         <v>0.0166824262105218</v>
       </c>
       <c r="M441" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N441" t="n">
-        <v>0.106382978723404</v>
+        <v>0.0654664484451719</v>
       </c>
       <c r="O441" t="b">
         <v>0</v>
@@ -22820,10 +22820,10 @@
         <v>0.0360420657677967</v>
       </c>
       <c r="M443" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N443" t="n">
-        <v>0.125397090787494</v>
+        <v>0.0668784484199967</v>
       </c>
       <c r="O443" t="b">
         <v>0</v>
@@ -22870,10 +22870,10 @@
         <v>0.0343605227223589</v>
       </c>
       <c r="M444" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N444" t="n">
-        <v>0.108774474256708</v>
+        <v>0.0725163161711385</v>
       </c>
       <c r="O444" t="b">
         <v>0</v>
@@ -22970,10 +22970,10 @@
         <v>0.0437208424765784</v>
       </c>
       <c r="M446" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N446" t="n">
-        <v>0.123071097226167</v>
+        <v>0.0662690523525514</v>
       </c>
       <c r="O446" t="b">
         <v>0</v>
@@ -23020,13 +23020,13 @@
         <v>0.0610065456886325</v>
       </c>
       <c r="M447" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N447" t="n">
-        <v>0.102660621096758</v>
+        <v>0.0684404140645051</v>
       </c>
       <c r="O447" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P447" t="b">
         <v>0</v>
@@ -23270,10 +23270,10 @@
         <v>0.0566385866157966</v>
       </c>
       <c r="M452" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N452" t="n">
-        <v>0.125372198714935</v>
+        <v>0.172386773233036</v>
       </c>
       <c r="O452" t="b">
         <v>0</v>
@@ -23320,10 +23320,10 @@
         <v>0.0285559013965602</v>
       </c>
       <c r="M453" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N453" t="n">
-        <v>0.104484809516155</v>
+        <v>0.160745860794085</v>
       </c>
       <c r="O453" t="b">
         <v>0</v>
@@ -23420,10 +23420,10 @@
         <v>0.046677766202464</v>
       </c>
       <c r="M455" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N455" t="n">
-        <v>0.123375555189998</v>
+        <v>0.172725777265998</v>
       </c>
       <c r="O455" t="b">
         <v>0</v>
@@ -23470,10 +23470,10 @@
         <v>0.0296242465483012</v>
       </c>
       <c r="M456" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="N456" t="n">
-        <v>0.0980761976612599</v>
+        <v>0.15843078083742</v>
       </c>
       <c r="O456" t="b">
         <v>0</v>
@@ -23570,10 +23570,10 @@
         <v>0.0552722507744152</v>
       </c>
       <c r="M458" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="N458" t="n">
-        <v>0.120964693430105</v>
+        <v>0.173886746805776</v>
       </c>
       <c r="O458" t="b">
         <v>0</v>
@@ -23620,10 +23620,10 @@
         <v>0.03098848965064</v>
       </c>
       <c r="M459" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="N459" t="n">
-        <v>0.0988593155893536</v>
+        <v>0.159695817490494</v>
       </c>
       <c r="O459" t="b">
         <v>0</v>
@@ -23720,10 +23720,10 @@
         <v>0.0538908498045714</v>
       </c>
       <c r="M461" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N461" t="n">
-        <v>0.119289874394779</v>
+        <v>0.168409234439688</v>
       </c>
       <c r="O461" t="b">
         <v>0</v>
@@ -23770,10 +23770,10 @@
         <v>0.0768061096222524</v>
       </c>
       <c r="M462" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N462" t="n">
-        <v>0.104948736578671</v>
+        <v>0.161459594736417</v>
       </c>
       <c r="O462" t="b">
         <v>0</v>
@@ -23870,10 +23870,10 @@
         <v>0.0453301855996467</v>
       </c>
       <c r="M464" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N464" t="n">
-        <v>0.125156445556946</v>
+        <v>0.175219023779725</v>
       </c>
       <c r="O464" t="b">
         <v>0</v>
@@ -23920,10 +23920,10 @@
         <v>0.0286634811152069</v>
       </c>
       <c r="M465" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N465" t="n">
-        <v>0.110265740434447</v>
+        <v>0.165398610651671</v>
       </c>
       <c r="O465" t="b">
         <v>0</v>
@@ -24020,10 +24020,10 @@
         <v>0.0724926808580702</v>
       </c>
       <c r="M467" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N467" t="n">
-        <v>0.126050420168067</v>
+        <v>0.178571428571429</v>
       </c>
       <c r="O467" t="b">
         <v>0</v>
@@ -24070,10 +24070,10 @@
         <v>0.0450646172100378</v>
       </c>
       <c r="M468" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N468" t="n">
-        <v>0.115995824150331</v>
+        <v>0.173993736225496</v>
       </c>
       <c r="O468" t="b">
         <v>0</v>
@@ -25070,10 +25070,10 @@
         <v>0.110430069440483</v>
       </c>
       <c r="M488" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N488" t="n">
-        <v>0.119415566170273</v>
+        <v>0.210733352065187</v>
       </c>
       <c r="O488" t="b">
         <v>0</v>
@@ -25220,10 +25220,10 @@
         <v>0.0389496885617358</v>
       </c>
       <c r="M491" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N491" t="n">
-        <v>0.121367887484829</v>
+        <v>0.214178624973228</v>
       </c>
       <c r="O491" t="b">
         <v>0</v>
@@ -25370,10 +25370,10 @@
         <v>0.0509466415658861</v>
       </c>
       <c r="M494" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="N494" t="n">
-        <v>0.124542124542125</v>
+        <v>0.212454212454212</v>
       </c>
       <c r="O494" t="b">
         <v>0</v>
@@ -25520,10 +25520,10 @@
         <v>0.0746246846655437</v>
       </c>
       <c r="M497" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N497" t="n">
-        <v>0.126752752911352</v>
+        <v>0.213895270537907</v>
       </c>
       <c r="O497" t="b">
         <v>0</v>
@@ -25670,10 +25670,10 @@
         <v>0.0477746421121876</v>
       </c>
       <c r="M500" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N500" t="n">
-        <v>0.119545726240287</v>
+        <v>0.212525735538288</v>
       </c>
       <c r="O500" t="b">
         <v>0</v>
